--- a/src/main/python/docs/测试集-answer-0517/batch_eval_result.xlsx
+++ b/src/main/python/docs/测试集-answer-0517/batch_eval_result.xlsx
@@ -463,7 +463,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-19 18:01:55</t>
+          <t>2026-05-20 16:20:41</t>
         </is>
       </c>
     </row>
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1054.094497842902</v>
+        <v>1160.064513065505</v>
       </c>
     </row>
     <row r="6">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>0.9718969555035128</v>
+        <v>0.9672131147540983</v>
       </c>
     </row>
     <row r="7">
@@ -585,7 +585,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{"2": 111, "4": 316}</t>
+          <t>{"2": 112, "4": 315}</t>
         </is>
       </c>
     </row>
@@ -610,7 +610,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1883.341999957338</v>
+        <v>2101.130124996416</v>
       </c>
     </row>
     <row r="19">
@@ -788,7 +788,7 @@
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>91.72495896928012</v>
+        <v>421.9184580724686</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>78.78666697070003</v>
+        <v>418.5417090775445</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>74.42924997303635</v>
+        <v>449.3575829546899</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>106.0985830845311</v>
+        <v>425.1913749612868</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -976,7 +976,7 @@
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>1984.577999915928</v>
+        <v>1995.137042016722</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>45.12474988587201</v>
+        <v>38.82875002454966</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>52.22320801112801</v>
+        <v>57.05462500918657</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -1119,7 +1119,7 @@
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>48.9961669081822</v>
+        <v>67.36470805481076</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -1166,7 +1166,7 @@
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>36.38145898003131</v>
+        <v>74.53629199881107</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1215,7 +1215,7 @@
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>1066.213291953318</v>
+        <v>1418.219291022979</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -1262,7 +1262,7 @@
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>27.8856250224635</v>
+        <v>148.9934590645134</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1309,7 +1309,7 @@
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>1374.060041038319</v>
+        <v>1854.881042032503</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>42.9327500751242</v>
+        <v>41.98424995411187</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -1403,7 +1403,7 @@
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>1151.659791008569</v>
+        <v>1708.841415937059</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -1450,7 +1450,7 @@
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>26.64599998388439</v>
+        <v>21.55950001906604</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -1497,7 +1497,7 @@
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>1466.388791915961</v>
+        <v>1387.597584049217</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -1512,7 +1512,7 @@
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t>[{"field": "familyInfo.familyrelation", "operator": "MATCH", "value": "子女"}, {"field": "familyInfo.familyclientbirthday", "operator": "RANGE", "value": {"max": "2023-05-19 23:59:59", "min": "2020-05-20 00:00:00"}}]</t>
+          <t>[{"field": "familyInfo.familyrelation", "operator": "MATCH", "value": "子女"}, {"field": "familyInfo.familyclientbirthday", "operator": "RANGE", "value": {"max": "2023-05-20 23:59:59", "min": "2020-05-21 00:00:00"}}]</t>
         </is>
       </c>
       <c r="O17" t="n">
@@ -1545,7 +1545,7 @@
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>949.6114170178771</v>
+        <v>1122.685250011273</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -1592,7 +1592,7 @@
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>17.8394999820739</v>
+        <v>32.78604196384549</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -1639,7 +1639,7 @@
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>20.550417015329</v>
+        <v>36.68687504250556</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -1686,7 +1686,7 @@
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>8.441541926003993</v>
+        <v>26.15029201842844</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -1733,7 +1733,7 @@
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>10.90129197109491</v>
+        <v>21.64958405774087</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -1780,7 +1780,7 @@
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>10.4115839349106</v>
+        <v>16.33570797275752</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -1827,7 +1827,7 @@
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>11.4293749211356</v>
+        <v>16.77379105240107</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -1874,7 +1874,7 @@
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>7.052375003695488</v>
+        <v>12.14295800309628</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -1921,7 +1921,7 @@
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>7.739417022094131</v>
+        <v>11.2919999519363</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -1968,7 +1968,7 @@
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>11.26158295664936</v>
+        <v>21.92174992524087</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -2015,7 +2015,7 @@
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>13.21891706902534</v>
+        <v>26.9479159032926</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
@@ -2062,7 +2062,7 @@
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>12.07829092163593</v>
+        <v>26.8213750096038</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
@@ -2109,7 +2109,7 @@
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>12.39587506279349</v>
+        <v>22.25649997126311</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
@@ -2156,7 +2156,7 @@
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>954.0619580075145</v>
+        <v>1113.343624980189</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
@@ -2203,7 +2203,7 @@
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>33.99725002236664</v>
+        <v>26.44666691776365</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
@@ -2250,7 +2250,7 @@
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>11.20212499517947</v>
+        <v>19.28604196291417</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
@@ -2297,7 +2297,7 @@
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>10.9261249890551</v>
+        <v>9.827250032685697</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>1429.378250031732</v>
+        <v>1015.346999978647</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
@@ -2391,7 +2391,7 @@
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>1446.74699997995</v>
+        <v>1284.117584000342</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
@@ -2438,7 +2438,7 @@
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>36.73304198309779</v>
+        <v>29.33666703756899</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
@@ -2485,7 +2485,7 @@
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>11.92770898342133</v>
+        <v>10.6543330475688</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
@@ -2532,7 +2532,7 @@
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>23.24549993500113</v>
+        <v>12.91545806452632</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
@@ -2579,7 +2579,7 @@
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>19.39220796339214</v>
+        <v>11.31004199851304</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
@@ -2626,7 +2626,7 @@
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>925.3620830131695</v>
+        <v>1272.012750036083</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
@@ -2673,7 +2673,7 @@
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>1176.536791026592</v>
+        <v>2504.983208025806</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
@@ -2720,7 +2720,7 @@
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>1041.406959062442</v>
+        <v>1156.148416921496</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
@@ -2767,7 +2767,7 @@
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>23.98891595657915</v>
+        <v>32.59008296299726</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
@@ -2814,7 +2814,7 @@
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>20.54304198827595</v>
+        <v>22.3657910246402</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
@@ -2861,7 +2861,7 @@
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>891.3885420188308</v>
+        <v>1222.143374965526</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
@@ -2908,7 +2908,7 @@
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>952.4566249456257</v>
+        <v>1460.070375003852</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
@@ -2955,7 +2955,7 @@
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>14.44745890330523</v>
+        <v>28.33541703876108</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
@@ -3002,7 +3002,7 @@
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>9.975082939490676</v>
+        <v>7.602290948852897</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
@@ -3049,7 +3049,7 @@
         <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>11.09420892316848</v>
+        <v>9.415916982106864</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
@@ -3096,7 +3096,7 @@
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>24.56445794086903</v>
+        <v>20.90129198040813</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
@@ -3143,7 +3143,7 @@
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>12.34675000887364</v>
+        <v>11.55458309222013</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
@@ -3190,7 +3190,7 @@
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>7.584750070236623</v>
+        <v>7.143790950067341</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
@@ -3237,7 +3237,7 @@
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>3724.846958997659</v>
+        <v>1861.988625023514</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
@@ -3252,7 +3252,7 @@
       </c>
       <c r="N54" s="3" t="inlineStr">
         <is>
-          <t>[{"field": "familyInfo.familyrelation", "operator": "MATCH", "value": "子女"}, {"field": "familyInfo.familyclientbirthday", "operator": "RANGE", "value": {"max": "2026-05-19 23:59:59", "min": "2008-05-20 00:00:00"}}]</t>
+          <t>[{"field": "familyInfo.familyrelation", "operator": "MATCH", "value": "子女"}, {"field": "familyInfo.familyclientbirthday", "operator": "RANGE", "value": {"max": "2026-05-20 23:59:59", "min": "2008-05-21 00:00:00"}}]</t>
         </is>
       </c>
       <c r="O54" t="n">
@@ -3285,7 +3285,7 @@
         <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>34.59170798305422</v>
+        <v>20.91491699684411</v>
       </c>
       <c r="J55" t="inlineStr">
         <is>
@@ -3332,7 +3332,7 @@
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>851.1389999184757</v>
+        <v>966.381625039503</v>
       </c>
       <c r="J56" t="inlineStr">
         <is>
@@ -3379,7 +3379,7 @@
         <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>921.7751249670982</v>
+        <v>915.2074169833213</v>
       </c>
       <c r="J57" t="inlineStr">
         <is>
@@ -3426,7 +3426,7 @@
         <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>16.44616608973593</v>
+        <v>18.59779108781368</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
@@ -3473,7 +3473,7 @@
         <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>2414.901167037897</v>
+        <v>1515.899957972579</v>
       </c>
       <c r="J59" t="inlineStr">
         <is>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="N59" s="3" t="inlineStr">
         <is>
-          <t>[{"field": "polNoInfo.plancodeinfo.abbrname", "operator": "CONTAINS", "value": ["百万任我行", "百万任我行17", "百万任我行18", "百万任我行22", "百万任我行23", "百万任我行25"]}]</t>
+          <t>[{"field": "polNoInfo.plancodeinfo.abbrname", "operator": "CONTAINS", "value": ["百万任我行", "百万任我行17", "百万任我行18", "百万任我行22", "百万任我行23", "百万任我行25", "倍享百万", "百万随行"]}]</t>
         </is>
       </c>
       <c r="O59" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="P59" s="3" t="inlineStr">
         <is>
-          <t>投保险种简称包含百万任我行、百万任我行17、百万任我行18、百万任我行22、百万任我行23、百万任我行25的客户</t>
+          <t>投保险种简称包含百万任我行、百万任我行17、百万任我行18、百万任我行22、百万任我行23、百万任我行25、倍享百万、百万随行的客户</t>
         </is>
       </c>
       <c r="Q59" t="inlineStr">
@@ -3520,7 +3520,7 @@
         <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>1248.008708003908</v>
+        <v>1025.441334000789</v>
       </c>
       <c r="J60" t="inlineStr">
         <is>
@@ -3567,7 +3567,7 @@
         <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>16.31583401467651</v>
+        <v>18.03204207681119</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
@@ -3614,7 +3614,7 @@
         <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>16.31370803806931</v>
+        <v>16.38070796616375</v>
       </c>
       <c r="J62" t="inlineStr">
         <is>
@@ -3661,7 +3661,7 @@
         <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>10.43399993795902</v>
+        <v>10.74658310972154</v>
       </c>
       <c r="J63" t="inlineStr">
         <is>
@@ -3708,7 +3708,7 @@
         <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>1496.121708070859</v>
+        <v>1312.658208073117</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
@@ -3755,7 +3755,7 @@
         <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>1004.740624921396</v>
+        <v>1024.985958007164</v>
       </c>
       <c r="J65" t="inlineStr">
         <is>
@@ -3802,7 +3802,7 @@
         <v>0</v>
       </c>
       <c r="H66" t="n">
-        <v>1258.858167100698</v>
+        <v>1757.861834019423</v>
       </c>
       <c r="J66" t="inlineStr">
         <is>
@@ -3851,7 +3851,7 @@
         <v>0</v>
       </c>
       <c r="H67" t="n">
-        <v>14.1263339901343</v>
+        <v>30.1390829263255</v>
       </c>
       <c r="J67" t="inlineStr">
         <is>
@@ -3899,7 +3899,7 @@
         <v>0</v>
       </c>
       <c r="H68" t="n">
-        <v>9.393416927196085</v>
+        <v>16.40841690823436</v>
       </c>
       <c r="J68" t="inlineStr">
         <is>
@@ -3947,7 +3947,7 @@
         <v>0</v>
       </c>
       <c r="H69" t="n">
-        <v>1228.38079102803</v>
+        <v>1443.31483298447</v>
       </c>
       <c r="J69" t="inlineStr">
         <is>
@@ -3994,7 +3994,7 @@
         <v>0</v>
       </c>
       <c r="H70" t="n">
-        <v>1609.234792063944</v>
+        <v>1081.77537494339</v>
       </c>
       <c r="J70" t="inlineStr">
         <is>
@@ -4041,7 +4041,7 @@
         <v>0</v>
       </c>
       <c r="H71" t="n">
-        <v>38.76200004015118</v>
+        <v>20.84974991157651</v>
       </c>
       <c r="J71" t="inlineStr">
         <is>
@@ -4088,7 +4088,7 @@
         <v>0</v>
       </c>
       <c r="H72" t="n">
-        <v>23.21333298459649</v>
+        <v>12.8675838932395</v>
       </c>
       <c r="J72" t="inlineStr">
         <is>
@@ -4136,7 +4136,7 @@
         <v>0</v>
       </c>
       <c r="H73" t="n">
-        <v>9.457957930862904</v>
+        <v>11.27258292399347</v>
       </c>
       <c r="J73" t="inlineStr">
         <is>
@@ -4183,7 +4183,7 @@
         <v>0</v>
       </c>
       <c r="H74" t="n">
-        <v>14.54133307561278</v>
+        <v>16.04162505827844</v>
       </c>
       <c r="J74" t="inlineStr">
         <is>
@@ -4230,7 +4230,7 @@
         <v>0</v>
       </c>
       <c r="H75" t="n">
-        <v>1541.273917071521</v>
+        <v>1471.29033296369</v>
       </c>
       <c r="J75" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
         <v>0</v>
       </c>
       <c r="H76" t="n">
-        <v>1626.762124942616</v>
+        <v>1686.074499972165</v>
       </c>
       <c r="J76" t="inlineStr">
         <is>
@@ -4292,7 +4292,7 @@
       </c>
       <c r="N76" s="3" t="inlineStr">
         <is>
-          <t>[{"field": "polNoInfo.plancodeinfo.planfullname", "operator": "NOT_CONTAINS", "value": ["养老保险"]}]</t>
+          <t>[{"field": "isBuyPension", "operator": "MATCH", "value": "没有购买"}]</t>
         </is>
       </c>
       <c r="O76" t="n">
@@ -4300,7 +4300,7 @@
       </c>
       <c r="P76" s="3" t="inlineStr">
         <is>
-          <t>投保险种名称不包含养老保险的客户</t>
+          <t>不是养老险客户</t>
         </is>
       </c>
       <c r="Q76" t="inlineStr">
@@ -4324,7 +4324,7 @@
         <v>0</v>
       </c>
       <c r="H77" t="n">
-        <v>1399.12583399564</v>
+        <v>2139.084708062001</v>
       </c>
       <c r="J77" t="inlineStr">
         <is>
@@ -4339,7 +4339,7 @@
       </c>
       <c r="N77" s="3" t="inlineStr">
         <is>
-          <t>[{"field": "dateCreated", "operator": "RANGE", "value": {"max": "2026-05-19 23:59:59", "min": "2026-04-19 00:00:00"}}]</t>
+          <t>[{"field": "dateCreated", "operator": "RANGE", "value": {"max": "2026-05-20 23:59:59", "min": "2026-04-20 00:00:00"}}]</t>
         </is>
       </c>
       <c r="O77" t="n">
@@ -4347,7 +4347,7 @@
       </c>
       <c r="P77" s="3" t="inlineStr">
         <is>
-          <t>客户添加日在2026-04-19 至 2026-05-19的客户</t>
+          <t>客户添加日在2026-04-20 至 2026-05-20的客户</t>
         </is>
       </c>
       <c r="Q77" t="inlineStr">
@@ -4371,7 +4371,7 @@
         <v>0</v>
       </c>
       <c r="H78" t="n">
-        <v>1333.369874977507</v>
+        <v>1377.109667053446</v>
       </c>
       <c r="J78" t="inlineStr">
         <is>
@@ -4386,7 +4386,7 @@
       </c>
       <c r="N78" s="3" t="inlineStr">
         <is>
-          <t>[{"field": "idValidDate", "operator": "RANGE", "value": {"max": "2026-06-19 00:00:00", "min": "2026-05-20 00:00:00"}}]</t>
+          <t>[{"field": "idValidDate", "operator": "RANGE", "value": {"max": "2026-06-20 00:00:00", "min": "2026-05-21 00:00:00"}}]</t>
         </is>
       </c>
       <c r="O78" t="n">
@@ -4394,7 +4394,7 @@
       </c>
       <c r="P78" s="3" t="inlineStr">
         <is>
-          <t>证件有效期在2026-05-20 至 2026-06-19的客户</t>
+          <t>证件有效期在2026-05-21 至 2026-06-20的客户</t>
         </is>
       </c>
       <c r="Q78" t="inlineStr">
@@ -4418,7 +4418,7 @@
         <v>0</v>
       </c>
       <c r="H79" t="n">
-        <v>28.4798750653863</v>
+        <v>28.67129095830023</v>
       </c>
       <c r="J79" t="inlineStr">
         <is>
@@ -4465,7 +4465,7 @@
         <v>0</v>
       </c>
       <c r="H80" t="n">
-        <v>23.21662497706711</v>
+        <v>15.89879207313061</v>
       </c>
       <c r="J80" t="inlineStr">
         <is>
@@ -4512,7 +4512,7 @@
         <v>0</v>
       </c>
       <c r="H81" t="n">
-        <v>1168.401250033639</v>
+        <v>1376.601833035238</v>
       </c>
       <c r="J81" t="inlineStr">
         <is>
@@ -4560,7 +4560,7 @@
         <v>0</v>
       </c>
       <c r="H82" t="n">
-        <v>1390.328875044361</v>
+        <v>2418.588000000454</v>
       </c>
       <c r="J82" t="inlineStr">
         <is>
@@ -4607,7 +4607,7 @@
         <v>0</v>
       </c>
       <c r="H83" t="n">
-        <v>1246.962041012011</v>
+        <v>1245.03970798105</v>
       </c>
       <c r="J83" t="inlineStr">
         <is>
@@ -4655,7 +4655,7 @@
         <v>0</v>
       </c>
       <c r="H84" t="n">
-        <v>1524.981082999147</v>
+        <v>2084.809334017336</v>
       </c>
       <c r="J84" t="inlineStr">
         <is>
@@ -4704,7 +4704,7 @@
         <v>0</v>
       </c>
       <c r="H85" t="n">
-        <v>17.5312920473516</v>
+        <v>23.41633301693946</v>
       </c>
       <c r="J85" t="inlineStr">
         <is>
@@ -4751,7 +4751,7 @@
         <v>0</v>
       </c>
       <c r="H86" t="n">
-        <v>11.83366600889713</v>
+        <v>15.40979195851833</v>
       </c>
       <c r="J86" t="inlineStr">
         <is>
@@ -4798,7 +4798,7 @@
         <v>0</v>
       </c>
       <c r="H87" t="n">
-        <v>17.43020804133266</v>
+        <v>19.5995420217514</v>
       </c>
       <c r="J87" t="inlineStr">
         <is>
@@ -4845,7 +4845,7 @@
         <v>0</v>
       </c>
       <c r="H88" t="n">
-        <v>13.46016698516905</v>
+        <v>14.71687504090369</v>
       </c>
       <c r="J88" t="inlineStr">
         <is>
@@ -4892,7 +4892,7 @@
         <v>0</v>
       </c>
       <c r="H89" t="n">
-        <v>1147.85591699183</v>
+        <v>1726.711625000462</v>
       </c>
       <c r="J89" t="inlineStr">
         <is>
@@ -4940,7 +4940,7 @@
         <v>0</v>
       </c>
       <c r="H90" t="n">
-        <v>1150.441625039093</v>
+        <v>1370.937125058845</v>
       </c>
       <c r="J90" t="inlineStr">
         <is>
@@ -4988,7 +4988,7 @@
         <v>0</v>
       </c>
       <c r="H91" t="n">
-        <v>1575.593916000798</v>
+        <v>1401.847625034861</v>
       </c>
       <c r="J91" t="inlineStr">
         <is>
@@ -5037,7 +5037,7 @@
         <v>0</v>
       </c>
       <c r="H92" t="n">
-        <v>978.5301659721881</v>
+        <v>1321.160957915708</v>
       </c>
       <c r="J92" t="inlineStr">
         <is>
@@ -5052,7 +5052,7 @@
       </c>
       <c r="N92" s="3" t="inlineStr">
         <is>
-          <t>[{"field": "polNoInfo.totmodalpremsum", "operator": "GTE", "value": 10000}]</t>
+          <t>[{"field": "annPremSegNum", "operator": "GTE", "value": 10000}]</t>
         </is>
       </c>
       <c r="O92" t="n">
@@ -5060,7 +5060,7 @@
       </c>
       <c r="P92" s="3" t="inlineStr">
         <is>
-          <t>期交保费≥10000的客户</t>
+          <t>年缴保费≥10000的客户</t>
         </is>
       </c>
       <c r="Q92" t="inlineStr">
@@ -5084,7 +5084,7 @@
         <v>0</v>
       </c>
       <c r="H93" t="n">
-        <v>18.80387496203184</v>
+        <v>59.40949998330325</v>
       </c>
       <c r="J93" t="inlineStr">
         <is>
@@ -5133,7 +5133,7 @@
         <v>0</v>
       </c>
       <c r="H94" t="n">
-        <v>12.48529204167426</v>
+        <v>30.98441695328802</v>
       </c>
       <c r="J94" t="inlineStr">
         <is>
@@ -5180,7 +5180,7 @@
         <v>0</v>
       </c>
       <c r="H95" t="n">
-        <v>1513.405416975729</v>
+        <v>1627.169082988985</v>
       </c>
       <c r="J95" t="inlineStr">
         <is>
@@ -5229,7 +5229,7 @@
         <v>0</v>
       </c>
       <c r="H96" t="n">
-        <v>1450.174874975346</v>
+        <v>1610.849124961533</v>
       </c>
       <c r="J96" t="inlineStr">
         <is>
@@ -5278,7 +5278,7 @@
         <v>0</v>
       </c>
       <c r="H97" t="n">
-        <v>24.53116700053215</v>
+        <v>29.8947918927297</v>
       </c>
       <c r="J97" t="inlineStr">
         <is>
@@ -5326,7 +5326,7 @@
         <v>0</v>
       </c>
       <c r="H98" t="n">
-        <v>28.39462505653501</v>
+        <v>26.63191698957235</v>
       </c>
       <c r="J98" t="inlineStr">
         <is>
@@ -5373,7 +5373,7 @@
         <v>0</v>
       </c>
       <c r="H99" t="n">
-        <v>22.41620793938637</v>
+        <v>21.38799999374896</v>
       </c>
       <c r="J99" t="inlineStr">
         <is>
@@ -5420,7 +5420,7 @@
         <v>0</v>
       </c>
       <c r="H100" t="n">
-        <v>23.34691700525582</v>
+        <v>16.95445808582008</v>
       </c>
       <c r="J100" t="inlineStr">
         <is>
@@ -5468,7 +5468,7 @@
         <v>0</v>
       </c>
       <c r="H101" t="n">
-        <v>1702.431292040274</v>
+        <v>1667.32474998571</v>
       </c>
       <c r="J101" t="inlineStr">
         <is>
@@ -5516,7 +5516,7 @@
         <v>0</v>
       </c>
       <c r="H102" t="n">
-        <v>24.09870899282396</v>
+        <v>35.75745900161564</v>
       </c>
       <c r="J102" t="inlineStr">
         <is>
@@ -5564,7 +5564,7 @@
         <v>0</v>
       </c>
       <c r="H103" t="n">
-        <v>24.92724999319762</v>
+        <v>14.56070900894701</v>
       </c>
       <c r="J103" t="inlineStr">
         <is>
@@ -5611,7 +5611,7 @@
         <v>0</v>
       </c>
       <c r="H104" t="n">
-        <v>12.78787502087653</v>
+        <v>12.75533298030496</v>
       </c>
       <c r="J104" t="inlineStr">
         <is>
@@ -5659,7 +5659,7 @@
         <v>0</v>
       </c>
       <c r="H105" t="n">
-        <v>2378.061500028707</v>
+        <v>1588.219000026584</v>
       </c>
       <c r="J105" t="inlineStr">
         <is>
@@ -5674,7 +5674,7 @@
       </c>
       <c r="N105" s="3" t="inlineStr">
         <is>
-          <t>[{"field": "isBuyInsurance", "operator": "CONTAINS", "value": ["客户", "准客"]}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="O105" t="n">
@@ -5682,7 +5682,7 @@
       </c>
       <c r="P105" s="3" t="inlineStr">
         <is>
-          <t>客户类型包含客户、准客的客户</t>
+          <t>提示：投保日期暂不支持搜索，无法进行查询。</t>
         </is>
       </c>
       <c r="Q105" t="inlineStr">
@@ -5706,7 +5706,7 @@
         <v>0</v>
       </c>
       <c r="H106" t="n">
-        <v>29.61270895320922</v>
+        <v>21.86512504704297</v>
       </c>
       <c r="J106" t="inlineStr">
         <is>
@@ -5753,7 +5753,7 @@
         <v>0</v>
       </c>
       <c r="H107" t="n">
-        <v>1744.115000008605</v>
+        <v>1729.01270899456</v>
       </c>
       <c r="J107" t="inlineStr">
         <is>
@@ -5802,7 +5802,7 @@
         <v>0</v>
       </c>
       <c r="H108" t="n">
-        <v>1499.332334031351</v>
+        <v>1497.161458013579</v>
       </c>
       <c r="J108" t="inlineStr">
         <is>
@@ -5851,7 +5851,7 @@
         <v>0</v>
       </c>
       <c r="H109" t="n">
-        <v>11.35233405511826</v>
+        <v>28.60962506383657</v>
       </c>
       <c r="J109" t="inlineStr">
         <is>
@@ -5898,7 +5898,7 @@
         <v>0</v>
       </c>
       <c r="H110" t="n">
-        <v>16.16708294022828</v>
+        <v>32.5952919665724</v>
       </c>
       <c r="J110" t="inlineStr">
         <is>
@@ -5947,7 +5947,7 @@
         <v>0</v>
       </c>
       <c r="H111" t="n">
-        <v>1217.492208001204</v>
+        <v>1559.899040963501</v>
       </c>
       <c r="J111" t="inlineStr">
         <is>
@@ -5997,7 +5997,7 @@
         <v>0</v>
       </c>
       <c r="H112" t="n">
-        <v>1925.367124960758</v>
+        <v>2137.937625055201</v>
       </c>
       <c r="J112" t="inlineStr">
         <is>
@@ -6046,7 +6046,7 @@
         <v>0</v>
       </c>
       <c r="H113" t="n">
-        <v>1891.957500018179</v>
+        <v>1793.043499928899</v>
       </c>
       <c r="J113" t="inlineStr">
         <is>
@@ -6093,7 +6093,7 @@
         <v>0</v>
       </c>
       <c r="H114" t="n">
-        <v>14.9030409520492</v>
+        <v>17.06387498416007</v>
       </c>
       <c r="J114" t="inlineStr">
         <is>
@@ -6140,7 +6140,7 @@
         <v>0</v>
       </c>
       <c r="H115" t="n">
-        <v>1420.009750057943</v>
+        <v>1307.776791974902</v>
       </c>
       <c r="J115" t="inlineStr">
         <is>
@@ -6189,7 +6189,7 @@
         <v>0</v>
       </c>
       <c r="H116" t="n">
-        <v>1350.693374988623</v>
+        <v>1301.303584012203</v>
       </c>
       <c r="J116" t="inlineStr">
         <is>
@@ -6237,7 +6237,7 @@
         <v>0</v>
       </c>
       <c r="H117" t="n">
-        <v>1126.25437497627</v>
+        <v>2357.905250042677</v>
       </c>
       <c r="J117" t="inlineStr">
         <is>
@@ -6285,7 +6285,7 @@
         <v>0</v>
       </c>
       <c r="H118" t="n">
-        <v>935.5195420794189</v>
+        <v>1135.637999977916</v>
       </c>
       <c r="J118" t="inlineStr">
         <is>
@@ -6300,7 +6300,7 @@
       </c>
       <c r="N118" s="3" t="inlineStr">
         <is>
-          <t>[{"field": "pCategorys", "operator": "CONTAINS", "value": ["疾病保险", "医疗保险"]}]</t>
+          <t>[{"field": "pCategorys", "operator": "MATCH", "value": "疾病保险"}, {"field": "pCategorys", "operator": "MATCH", "value": "医疗保险"}]</t>
         </is>
       </c>
       <c r="O118" t="n">
@@ -6308,7 +6308,8 @@
       </c>
       <c r="P118" s="3" t="inlineStr">
         <is>
-          <t>产品类别包含疾病保险、医疗保险的客户</t>
+          <t>产品类别为疾病保险
+并且产品类别为医疗保险的客户</t>
         </is>
       </c>
       <c r="Q118" t="inlineStr">
@@ -6332,7 +6333,7 @@
         <v>0</v>
       </c>
       <c r="H119" t="n">
-        <v>12.86008302122355</v>
+        <v>24.89250001963228</v>
       </c>
       <c r="J119" t="inlineStr">
         <is>
@@ -6380,7 +6381,7 @@
         <v>0</v>
       </c>
       <c r="H120" t="n">
-        <v>20.50833299290389</v>
+        <v>31.19870903901756</v>
       </c>
       <c r="J120" t="inlineStr">
         <is>
@@ -6427,7 +6428,7 @@
         <v>0</v>
       </c>
       <c r="H121" t="n">
-        <v>17.37816608510911</v>
+        <v>11.41462498344481</v>
       </c>
       <c r="J121" t="inlineStr">
         <is>
@@ -6474,7 +6475,7 @@
         <v>0</v>
       </c>
       <c r="H122" t="n">
-        <v>1046.177916927263</v>
+        <v>1416.555957985111</v>
       </c>
       <c r="J122" t="inlineStr">
         <is>
@@ -6522,7 +6523,7 @@
         <v>0</v>
       </c>
       <c r="H123" t="n">
-        <v>1121.420791954733</v>
+        <v>1452.047874918208</v>
       </c>
       <c r="J123" t="inlineStr">
         <is>
@@ -6570,7 +6571,7 @@
         <v>0</v>
       </c>
       <c r="H124" t="n">
-        <v>21.78125001955777</v>
+        <v>20.52925003226846</v>
       </c>
       <c r="J124" t="inlineStr">
         <is>
@@ -6617,7 +6618,7 @@
         <v>0</v>
       </c>
       <c r="H125" t="n">
-        <v>1190.804457990453</v>
+        <v>1397.184666944668</v>
       </c>
       <c r="J125" t="inlineStr">
         <is>
@@ -6664,7 +6665,7 @@
         <v>0</v>
       </c>
       <c r="H126" t="n">
-        <v>1224.127916968428</v>
+        <v>1263.894166098908</v>
       </c>
       <c r="J126" t="inlineStr">
         <is>
@@ -6712,7 +6713,7 @@
         <v>0</v>
       </c>
       <c r="H127" t="n">
-        <v>20.00033296644688</v>
+        <v>31.21204196941108</v>
       </c>
       <c r="J127" t="inlineStr">
         <is>
@@ -6759,7 +6760,7 @@
         <v>0</v>
       </c>
       <c r="H128" t="n">
-        <v>1033.615042106248</v>
+        <v>1154.489500098862</v>
       </c>
       <c r="J128" t="inlineStr">
         <is>
@@ -6774,7 +6775,7 @@
       </c>
       <c r="N128" s="3" t="inlineStr">
         <is>
-          <t>[{"field": "annPremSegNum", "operator": "GTE", "value": 200000}, {"field": "effAppEndDate", "operator": "LTE", "value": "2026-05-19"}]</t>
+          <t>[{"field": "annPremSegNum", "operator": "GTE", "value": 200000}, {"field": "effAppEndDate", "operator": "LTE", "value": "2026-05-20"}]</t>
         </is>
       </c>
       <c r="O128" t="n">
@@ -6783,7 +6784,7 @@
       <c r="P128" s="3" t="inlineStr">
         <is>
           <t>年缴保费≥200000
-并且缴费期满日≤2026-05-19的客户</t>
+并且缴费期满日≤2026-05-20的客户</t>
         </is>
       </c>
       <c r="Q128" t="inlineStr">
@@ -6807,7 +6808,7 @@
         <v>0</v>
       </c>
       <c r="H129" t="n">
-        <v>11.8687089998275</v>
+        <v>12.99662503879517</v>
       </c>
       <c r="J129" t="inlineStr">
         <is>
@@ -6854,7 +6855,7 @@
         <v>0</v>
       </c>
       <c r="H130" t="n">
-        <v>1216.042874963023</v>
+        <v>13.5982499923557</v>
       </c>
       <c r="J130" t="inlineStr">
         <is>
@@ -6873,7 +6874,7 @@
         </is>
       </c>
       <c r="O130" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P130" s="3" t="inlineStr">
         <is>
@@ -6901,7 +6902,7 @@
         <v>0</v>
       </c>
       <c r="H131" t="n">
-        <v>22.1437499858439</v>
+        <v>12.47158297337592</v>
       </c>
       <c r="J131" t="inlineStr">
         <is>
@@ -6948,7 +6949,7 @@
         <v>0</v>
       </c>
       <c r="H132" t="n">
-        <v>12.77050003409386</v>
+        <v>12.09491700865328</v>
       </c>
       <c r="J132" t="inlineStr">
         <is>
@@ -6963,7 +6964,7 @@
       </c>
       <c r="N132" s="3" t="inlineStr">
         <is>
-          <t>[{"field": "familyInfo.familyclientbirthday", "operator": "RANGE", "value": {"max": "2020-05-19 23:59:59", "min": "2013-05-20 00:00:00"}}, {"field": "familyInfo.familyrelation", "operator": "MATCH", "value": "子女"}]</t>
+          <t>[{"field": "familyInfo.familyclientbirthday", "operator": "RANGE", "value": {"max": "2020-05-20 23:59:59", "min": "2013-05-21 00:00:00"}}, {"field": "familyInfo.familyrelation", "operator": "MATCH", "value": "子女"}]</t>
         </is>
       </c>
       <c r="O132" t="n">
@@ -6996,7 +6997,7 @@
         <v>0</v>
       </c>
       <c r="H133" t="n">
-        <v>986.8012079969049</v>
+        <v>1242.207083036192</v>
       </c>
       <c r="J133" t="inlineStr">
         <is>
@@ -7043,7 +7044,7 @@
         <v>0</v>
       </c>
       <c r="H134" t="n">
-        <v>1344.062458025292</v>
+        <v>1209.495750023052</v>
       </c>
       <c r="J134" t="inlineStr">
         <is>
@@ -7091,7 +7092,7 @@
         <v>0</v>
       </c>
       <c r="H135" t="n">
-        <v>24.6662909630686</v>
+        <v>21.14045806229115</v>
       </c>
       <c r="J135" t="inlineStr">
         <is>
@@ -7138,7 +7139,7 @@
         <v>0</v>
       </c>
       <c r="H136" t="n">
-        <v>1268.523290986195</v>
+        <v>1380.992666003294</v>
       </c>
       <c r="J136" t="inlineStr">
         <is>
@@ -7186,7 +7187,7 @@
         <v>0</v>
       </c>
       <c r="H137" t="n">
-        <v>10.87970903608948</v>
+        <v>16.72491698991507</v>
       </c>
       <c r="J137" t="inlineStr">
         <is>
@@ -7233,7 +7234,7 @@
         <v>0</v>
       </c>
       <c r="H138" t="n">
-        <v>11.07495801988989</v>
+        <v>10.8600000385195</v>
       </c>
       <c r="J138" t="inlineStr">
         <is>
@@ -7281,7 +7282,7 @@
         <v>0</v>
       </c>
       <c r="H139" t="n">
-        <v>1058.732583071105</v>
+        <v>1590.134499943815</v>
       </c>
       <c r="J139" t="inlineStr">
         <is>
@@ -7329,7 +7330,7 @@
         <v>0</v>
       </c>
       <c r="H140" t="n">
-        <v>997.8413750650361</v>
+        <v>1092.371082981117</v>
       </c>
       <c r="J140" t="inlineStr">
         <is>
@@ -7376,7 +7377,7 @@
         <v>0</v>
       </c>
       <c r="H141" t="n">
-        <v>1431.422458961606</v>
+        <v>1676.317582954653</v>
       </c>
       <c r="J141" t="inlineStr">
         <is>
@@ -7423,7 +7424,7 @@
         <v>0</v>
       </c>
       <c r="H142" t="n">
-        <v>35.5424580629915</v>
+        <v>21.69333293568343</v>
       </c>
       <c r="J142" t="inlineStr">
         <is>
@@ -7470,7 +7471,7 @@
         <v>0</v>
       </c>
       <c r="H143" t="n">
-        <v>17.93358300346881</v>
+        <v>15.60479192994535</v>
       </c>
       <c r="J143" t="inlineStr">
         <is>
@@ -7517,7 +7518,7 @@
         <v>0</v>
       </c>
       <c r="H144" t="n">
-        <v>15.06741601042449</v>
+        <v>10.51254104822874</v>
       </c>
       <c r="J144" t="inlineStr">
         <is>
@@ -7564,7 +7565,7 @@
         <v>0</v>
       </c>
       <c r="H145" t="n">
-        <v>15.06583299487829</v>
+        <v>12.06737500615418</v>
       </c>
       <c r="J145" t="inlineStr">
         <is>
@@ -7611,7 +7612,7 @@
         <v>0</v>
       </c>
       <c r="H146" t="n">
-        <v>1091.49908402469</v>
+        <v>1564.706790959463</v>
       </c>
       <c r="J146" t="inlineStr">
         <is>
@@ -7658,7 +7659,7 @@
         <v>0</v>
       </c>
       <c r="H147" t="n">
-        <v>1701.57641696278</v>
+        <v>1376.666833064519</v>
       </c>
       <c r="J147" t="inlineStr">
         <is>
@@ -7705,7 +7706,7 @@
         <v>0</v>
       </c>
       <c r="H148" t="n">
-        <v>1287.304832949303</v>
+        <v>1177.858124952763</v>
       </c>
       <c r="J148" t="inlineStr">
         <is>
@@ -7753,7 +7754,7 @@
         <v>0</v>
       </c>
       <c r="H149" t="n">
-        <v>1143.202416948043</v>
+        <v>1525.10958397761</v>
       </c>
       <c r="J149" t="inlineStr">
         <is>
@@ -7801,7 +7802,7 @@
         <v>0</v>
       </c>
       <c r="H150" t="n">
-        <v>1367.313708062284</v>
+        <v>1615.204375004396</v>
       </c>
       <c r="J150" t="inlineStr">
         <is>
@@ -7850,7 +7851,7 @@
         <v>0</v>
       </c>
       <c r="H151" t="n">
-        <v>1914.757833001204</v>
+        <v>1628.951499937102</v>
       </c>
       <c r="J151" t="inlineStr">
         <is>
@@ -7865,7 +7866,7 @@
       </c>
       <c r="N151" s="3" t="inlineStr">
         <is>
-          <t>[{"field": "newValueLabel", "operator": "CONTAINS", "value": ["A1", "A2", "A3", "A4"]}, {"field": "familyInfo.familyrelation", "operator": "MATCH", "value": "子女"}, {"field": "familyInfo.familyclientbirthday", "operator": "RANGE", "value": {"max": "2026-05-19 23:59:59", "min": "2008-05-20 00:00:00"}}]</t>
+          <t>[{"field": "newValueLabel", "operator": "CONTAINS", "value": ["A1", "A2", "A3", "A4"]}, {"field": "familyInfo.familyrelation", "operator": "MATCH", "value": "子女"}, {"field": "familyInfo.familyclientbirthday", "operator": "RANGE", "value": {"max": "2026-05-20 23:59:59", "min": "2008-05-21 00:00:00"}}]</t>
         </is>
       </c>
       <c r="O151" t="n">
@@ -7899,7 +7900,7 @@
         <v>0</v>
       </c>
       <c r="H152" t="n">
-        <v>22.88137504365295</v>
+        <v>27.11520798038691</v>
       </c>
       <c r="J152" t="inlineStr">
         <is>
@@ -7914,7 +7915,7 @@
       </c>
       <c r="N152" s="3" t="inlineStr">
         <is>
-          <t>[{"field": "familyInfo.familyclientbirthday", "operator": "LTE", "value": "1956-05-19 23:59:59"}, {"field": "familyInfo.familyrelation", "operator": "MATCH", "value": "父母"}]</t>
+          <t>[{"field": "familyInfo.familyclientbirthday", "operator": "LTE", "value": "1956-05-20 23:59:59"}, {"field": "familyInfo.familyrelation", "operator": "MATCH", "value": "父母"}]</t>
         </is>
       </c>
       <c r="O152" t="n">
@@ -7947,7 +7948,7 @@
         <v>0</v>
       </c>
       <c r="H153" t="n">
-        <v>1459.592500003055</v>
+        <v>2082.863582996652</v>
       </c>
       <c r="J153" t="inlineStr">
         <is>
@@ -7997,7 +7998,7 @@
         <v>0</v>
       </c>
       <c r="H154" t="n">
-        <v>40.61883292160928</v>
+        <v>23.61770893912762</v>
       </c>
       <c r="J154" t="inlineStr">
         <is>
@@ -8044,7 +8045,7 @@
         <v>0</v>
       </c>
       <c r="H155" t="n">
-        <v>45.36500002723187</v>
+        <v>30.29141703154892</v>
       </c>
       <c r="J155" t="inlineStr">
         <is>
@@ -8091,7 +8092,7 @@
         <v>0</v>
       </c>
       <c r="H156" t="n">
-        <v>17.18466600868851</v>
+        <v>14.62429098319262</v>
       </c>
       <c r="J156" t="inlineStr">
         <is>
@@ -8138,7 +8139,7 @@
         <v>0</v>
       </c>
       <c r="H157" t="n">
-        <v>31.24525002203882</v>
+        <v>15.81166696269065</v>
       </c>
       <c r="J157" t="inlineStr">
         <is>
@@ -8185,7 +8186,7 @@
         <v>0</v>
       </c>
       <c r="H158" t="n">
-        <v>16.06166700366884</v>
+        <v>11.26033300533891</v>
       </c>
       <c r="J158" t="inlineStr">
         <is>
@@ -8232,7 +8233,7 @@
         <v>0</v>
       </c>
       <c r="H159" t="n">
-        <v>1376.079125097021</v>
+        <v>1198.935625026934</v>
       </c>
       <c r="J159" t="inlineStr">
         <is>
@@ -8279,7 +8280,7 @@
         <v>0</v>
       </c>
       <c r="H160" t="n">
-        <v>2474.868583027273</v>
+        <v>1392.503499984741</v>
       </c>
       <c r="J160" t="inlineStr">
         <is>
@@ -8294,7 +8295,7 @@
       </c>
       <c r="N160" s="3" t="inlineStr">
         <is>
-          <t>[{"field": "familyInfo.familyrelation", "operator": "MATCH", "value": "子女"}, {"field": "familyInfo.familyclientbirthday", "operator": "RANGE", "value": {"max": "2026-05-19 23:59:59", "min": "2008-05-20 00:00:00"}}]</t>
+          <t>[{"field": "familyInfo.familyrelation", "operator": "MATCH", "value": "子女"}, {"field": "familyInfo.familyclientbirthday", "operator": "RANGE", "value": {"max": "2026-05-20 23:59:59", "min": "2008-05-21 00:00:00"}}]</t>
         </is>
       </c>
       <c r="O160" t="n">
@@ -8327,7 +8328,7 @@
         <v>0</v>
       </c>
       <c r="H161" t="n">
-        <v>18.87391600757837</v>
+        <v>24.67620803508908</v>
       </c>
       <c r="J161" t="inlineStr">
         <is>
@@ -8374,7 +8375,7 @@
         <v>0</v>
       </c>
       <c r="H162" t="n">
-        <v>23.24641693849117</v>
+        <v>13.38841603137553</v>
       </c>
       <c r="J162" t="inlineStr">
         <is>
@@ -8422,7 +8423,7 @@
         <v>0</v>
       </c>
       <c r="H163" t="n">
-        <v>11.6660000057891</v>
+        <v>12.07020797301084</v>
       </c>
       <c r="J163" t="inlineStr">
         <is>
@@ -8469,7 +8470,7 @@
         <v>0</v>
       </c>
       <c r="H164" t="n">
-        <v>922.6480409270152</v>
+        <v>1203.229125007056</v>
       </c>
       <c r="J164" t="inlineStr">
         <is>
@@ -8516,7 +8517,7 @@
         <v>0</v>
       </c>
       <c r="H165" t="n">
-        <v>16.97050000075251</v>
+        <v>32.79624995775521</v>
       </c>
       <c r="J165" t="inlineStr">
         <is>
@@ -8563,7 +8564,7 @@
         <v>0</v>
       </c>
       <c r="H166" t="n">
-        <v>10.56166598573327</v>
+        <v>15.28558402787894</v>
       </c>
       <c r="J166" t="inlineStr">
         <is>
@@ -8610,7 +8611,7 @@
         <v>0</v>
       </c>
       <c r="H167" t="n">
-        <v>11.98595797177404</v>
+        <v>12.85058399662375</v>
       </c>
       <c r="J167" t="inlineStr">
         <is>
@@ -8657,7 +8658,7 @@
         <v>0</v>
       </c>
       <c r="H168" t="n">
-        <v>1022.703999886289</v>
+        <v>1294.723915983923</v>
       </c>
       <c r="J168" t="inlineStr">
         <is>
@@ -8705,7 +8706,7 @@
         <v>0</v>
       </c>
       <c r="H169" t="n">
-        <v>1373.381834011525</v>
+        <v>1672.088916995563</v>
       </c>
       <c r="J169" t="inlineStr">
         <is>
@@ -8720,7 +8721,7 @@
       </c>
       <c r="N169" s="3" t="inlineStr">
         <is>
-          <t>[{"field": "familyInfo.familyrelation", "operator": "MATCH", "value": "子女"}, {"field": "familyInfo.familyclientbirthday", "operator": "RANGE", "value": {"max": "2026-05-19 23:59:59", "min": "2008-05-20 00:00:00"}}, {"field": "polNoInfo.plancodeinfo.abbrname", "operator": "NOT_CONTAINS", "value": ["学平险"]}]</t>
+          <t>[{"field": "familyInfo.familyrelation", "operator": "MATCH", "value": "子女"}, {"field": "familyInfo.familyclientbirthday", "operator": "RANGE", "value": {"max": "2026-05-20 23:59:59", "min": "2008-05-21 00:00:00"}}, {"field": "polNoInfo.plancodeinfo.abbrname", "operator": "NOT_CONTAINS", "value": ["学平险"]}]</t>
         </is>
       </c>
       <c r="O169" t="n">
@@ -8754,7 +8755,7 @@
         <v>0</v>
       </c>
       <c r="H170" t="n">
-        <v>959.7669579088688</v>
+        <v>1188.135999953374</v>
       </c>
       <c r="J170" t="inlineStr">
         <is>
@@ -8801,7 +8802,7 @@
         <v>0</v>
       </c>
       <c r="H171" t="n">
-        <v>1261.77666708827</v>
+        <v>1436.474791029468</v>
       </c>
       <c r="J171" t="inlineStr">
         <is>
@@ -8816,7 +8817,7 @@
       </c>
       <c r="N171" s="3" t="inlineStr">
         <is>
-          <t>[{"field": "agentPerspProductType", "operator": "EXISTS", "value": ""}, {"field": "planAbbrNames", "operator": "NOT_EXISTS", "value": ""}]</t>
+          <t>[{"field": "agentPerspProductType", "operator": "EXISTS", "value": ""}, {"field": "planAbbrNames", "operator": "NOT_CONTAINS", "value": ["寿险"]}]</t>
         </is>
       </c>
       <c r="O171" t="n">
@@ -8825,7 +8826,7 @@
       <c r="P171" s="3" t="inlineStr">
         <is>
           <t>有综拓产品类别
-并且没有寿险产品的客户</t>
+并且寿险产品不包含寿险的客户</t>
         </is>
       </c>
       <c r="Q171" t="inlineStr">
@@ -8849,7 +8850,7 @@
         <v>0</v>
       </c>
       <c r="H172" t="n">
-        <v>1024.6822910849</v>
+        <v>1774.032915942371</v>
       </c>
       <c r="J172" t="inlineStr">
         <is>
@@ -8896,7 +8897,7 @@
         <v>0</v>
       </c>
       <c r="H173" t="n">
-        <v>1221.382040996104</v>
+        <v>1231.259541003965</v>
       </c>
       <c r="J173" t="inlineStr">
         <is>
@@ -8943,7 +8944,7 @@
         <v>0</v>
       </c>
       <c r="H174" t="n">
-        <v>47.5178329506889</v>
+        <v>17.76333304587752</v>
       </c>
       <c r="J174" t="inlineStr">
         <is>
@@ -8958,7 +8959,7 @@
       </c>
       <c r="N174" s="3" t="inlineStr">
         <is>
-          <t>[{"field": "polNoInfo.plancodeinfo.abbrname", "operator": "MATCH", "value": "e生保"}, {"field": "validSinsMatuDateTime", "operator": "RANGE", "value": {"max": "2026-06-16", "min": "2026-05-19"}}]</t>
+          <t>[{"field": "polNoInfo.plancodeinfo.abbrname", "operator": "MATCH", "value": "e生保"}, {"field": "validSinsMatuDateTime", "operator": "RANGE", "value": {"max": "2026-06-17", "min": "2026-05-20"}}]</t>
         </is>
       </c>
       <c r="O174" t="n">
@@ -8967,7 +8968,7 @@
       <c r="P174" s="3" t="inlineStr">
         <is>
           <t>投保险种简称为e生保
-并且保单到期日在2026-05-19 至 2026-06-16的客户</t>
+并且保单到期日在2026-05-20 至 2026-06-17的客户</t>
         </is>
       </c>
       <c r="Q174" t="inlineStr">
@@ -8991,7 +8992,7 @@
         <v>0</v>
       </c>
       <c r="H175" t="n">
-        <v>1382.516999961808</v>
+        <v>1658.005957957357</v>
       </c>
       <c r="J175" t="inlineStr">
         <is>
@@ -9040,7 +9041,7 @@
         <v>0</v>
       </c>
       <c r="H176" t="n">
-        <v>1883.341999957338</v>
+        <v>1913.80433307495</v>
       </c>
       <c r="J176" t="inlineStr">
         <is>
@@ -9088,7 +9089,7 @@
         <v>0</v>
       </c>
       <c r="H177" t="n">
-        <v>1437.052041990682</v>
+        <v>1314.700625021942</v>
       </c>
       <c r="J177" t="inlineStr">
         <is>
@@ -9136,7 +9137,7 @@
         <v>0</v>
       </c>
       <c r="H178" t="n">
-        <v>1222.188457963057</v>
+        <v>1397.179499967024</v>
       </c>
       <c r="J178" t="inlineStr">
         <is>
@@ -9185,7 +9186,7 @@
         <v>0</v>
       </c>
       <c r="H179" t="n">
-        <v>1463.8096250128</v>
+        <v>1636.678040958941</v>
       </c>
       <c r="J179" t="inlineStr">
         <is>
@@ -9234,7 +9235,7 @@
         <v>0</v>
       </c>
       <c r="H180" t="n">
-        <v>1197.433833964169</v>
+        <v>1330.414874944836</v>
       </c>
       <c r="J180" t="inlineStr">
         <is>
@@ -9281,7 +9282,7 @@
         <v>0</v>
       </c>
       <c r="H181" t="n">
-        <v>1957.344082999043</v>
+        <v>1708.036207943223</v>
       </c>
       <c r="J181" t="inlineStr">
         <is>
@@ -9330,7 +9331,7 @@
         <v>0</v>
       </c>
       <c r="H182" t="n">
-        <v>1358.6035000626</v>
+        <v>1751.944415969774</v>
       </c>
       <c r="J182" t="inlineStr">
         <is>
@@ -9379,7 +9380,7 @@
         <v>0</v>
       </c>
       <c r="H183" t="n">
-        <v>1569.50987491291</v>
+        <v>1914.86708400771</v>
       </c>
       <c r="J183" t="inlineStr">
         <is>
@@ -9428,7 +9429,7 @@
         <v>0</v>
       </c>
       <c r="H184" t="n">
-        <v>1085.980582982302</v>
+        <v>1282.135916990228</v>
       </c>
       <c r="J184" t="inlineStr">
         <is>
@@ -9476,7 +9477,7 @@
         <v>0</v>
       </c>
       <c r="H185" t="n">
-        <v>1502.554832957685</v>
+        <v>1696.643832954578</v>
       </c>
       <c r="J185" t="inlineStr">
         <is>
@@ -9525,7 +9526,7 @@
         <v>0</v>
       </c>
       <c r="H186" t="n">
-        <v>1498.905040905811</v>
+        <v>1702.024207916111</v>
       </c>
       <c r="J186" t="inlineStr">
         <is>
@@ -9574,7 +9575,7 @@
         <v>0</v>
       </c>
       <c r="H187" t="n">
-        <v>1218.61933299806</v>
+        <v>1446.51437504217</v>
       </c>
       <c r="J187" t="inlineStr">
         <is>
@@ -9622,7 +9623,7 @@
         <v>0</v>
       </c>
       <c r="H188" t="n">
-        <v>1438.203749945387</v>
+        <v>1592.770667048171</v>
       </c>
       <c r="J188" t="inlineStr">
         <is>
@@ -9671,7 +9672,7 @@
         <v>0</v>
       </c>
       <c r="H189" t="n">
-        <v>1289.312915992923</v>
+        <v>1649.643832934089</v>
       </c>
       <c r="J189" t="inlineStr">
         <is>
@@ -9718,7 +9719,7 @@
         <v>0</v>
       </c>
       <c r="H190" t="n">
-        <v>16.79220795631409</v>
+        <v>15.38412505760789</v>
       </c>
       <c r="J190" t="inlineStr">
         <is>
@@ -9766,7 +9767,7 @@
         <v>0</v>
       </c>
       <c r="H191" t="n">
-        <v>1225.912958034314</v>
+        <v>1472.516332985833</v>
       </c>
       <c r="J191" t="inlineStr">
         <is>
@@ -9814,7 +9815,7 @@
         <v>0</v>
       </c>
       <c r="H192" t="n">
-        <v>1750.942999962717</v>
+        <v>1431.168457958847</v>
       </c>
       <c r="J192" t="inlineStr">
         <is>
@@ -9829,7 +9830,7 @@
       </c>
       <c r="N192" s="3" t="inlineStr">
         <is>
-          <t>[{"field": "polNoInfo.polStatus", "operator": "MATCH", "value": "犹豫期退保"}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="O192" t="n">
@@ -9837,8 +9838,7 @@
       </c>
       <c r="P192" s="3" t="inlineStr">
         <is>
-          <t>保单状态为犹豫期退保的客户
-提示：犹豫期时间暂不支持搜索，系统将按可支持字段搜索。</t>
+          <t>提示：犹豫期时间暂不支持搜索，无法进行查询。</t>
         </is>
       </c>
       <c r="Q192" t="inlineStr">
@@ -9862,7 +9862,7 @@
         <v>0</v>
       </c>
       <c r="H193" t="n">
-        <v>1292.347791953944</v>
+        <v>1499.247375060804</v>
       </c>
       <c r="J193" t="inlineStr">
         <is>
@@ -9877,7 +9877,7 @@
       </c>
       <c r="N193" s="3" t="inlineStr">
         <is>
-          <t>[{"field": "effAppEndDate", "operator": "LTE", "value": "2026-05-19"}, {"field": "newValueLabel", "operator": "CONTAINS", "value": ["A1", "A2", "A3", "A4", "B", "C"]}]</t>
+          <t>[{"field": "effAppEndDate", "operator": "LTE", "value": "2026-05-20"}, {"field": "newValueLabel", "operator": "CONTAINS", "value": ["A1", "A2", "A3", "A4", "B", "C"]}]</t>
         </is>
       </c>
       <c r="O193" t="n">
@@ -9885,7 +9885,7 @@
       </c>
       <c r="P193" s="3" t="inlineStr">
         <is>
-          <t>缴费期满日≤2026-05-19
+          <t>缴费期满日≤2026-05-20
 并且客户价值标签包含A1、A2、A3、A4、B、C的客户</t>
         </is>
       </c>
@@ -9910,7 +9910,7 @@
         <v>0</v>
       </c>
       <c r="H194" t="n">
-        <v>1455.467917025089</v>
+        <v>1696.570207946934</v>
       </c>
       <c r="J194" t="inlineStr">
         <is>
@@ -9957,7 +9957,7 @@
         <v>0</v>
       </c>
       <c r="H195" t="n">
-        <v>1351.718459045514</v>
+        <v>1308.319209027104</v>
       </c>
       <c r="J195" t="inlineStr">
         <is>
@@ -9972,7 +9972,7 @@
       </c>
       <c r="N195" s="3" t="inlineStr">
         <is>
-          <t>[{"field": "dateCreated", "operator": "RANGE", "value": {"max": "2026-05-19 23:59:59", "min": "2026-04-19 00:00:00"}}]</t>
+          <t>[{"field": "dateCreated", "operator": "RANGE", "value": {"max": "2026-05-20 23:59:59", "min": "2026-04-20 00:00:00"}}]</t>
         </is>
       </c>
       <c r="O195" t="n">
@@ -9980,7 +9980,7 @@
       </c>
       <c r="P195" s="3" t="inlineStr">
         <is>
-          <t>客户添加日在2026-04-19 至 2026-05-19的客户</t>
+          <t>客户添加日在2026-04-20 至 2026-05-20的客户</t>
         </is>
       </c>
       <c r="Q195" t="inlineStr">
@@ -10004,7 +10004,7 @@
         <v>0</v>
       </c>
       <c r="H196" t="n">
-        <v>1420.413083978929</v>
+        <v>1671.242875047028</v>
       </c>
       <c r="J196" t="inlineStr">
         <is>
@@ -10051,7 +10051,7 @@
         <v>0</v>
       </c>
       <c r="H197" t="n">
-        <v>1550.253333989531</v>
+        <v>2408.095375052653</v>
       </c>
       <c r="J197" t="inlineStr">
         <is>
@@ -10098,7 +10098,7 @@
         <v>0</v>
       </c>
       <c r="H198" t="n">
-        <v>1416.0134580452</v>
+        <v>1535.651791957207</v>
       </c>
       <c r="J198" t="inlineStr">
         <is>
@@ -10145,7 +10145,7 @@
         <v>0</v>
       </c>
       <c r="H199" t="n">
-        <v>33.21937494911253</v>
+        <v>31.15166700445116</v>
       </c>
       <c r="J199" t="inlineStr">
         <is>
@@ -10192,7 +10192,7 @@
         <v>0</v>
       </c>
       <c r="H200" t="n">
-        <v>1131.367124966346</v>
+        <v>1232.012707972899</v>
       </c>
       <c r="J200" t="inlineStr">
         <is>
@@ -10239,7 +10239,7 @@
         <v>0</v>
       </c>
       <c r="H201" t="n">
-        <v>1193.081624922343</v>
+        <v>1192.780458950438</v>
       </c>
       <c r="J201" t="inlineStr">
         <is>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="N201" s="3" t="inlineStr">
         <is>
-          <t>[{"field": "validSinsMatuDateTime", "operator": "RANGE", "value": {"max": "2026-06-19", "min": "2026-05-19"}}]</t>
+          <t>[{"field": "validSinsMatuDateTime", "operator": "RANGE", "value": {"max": "2026-06-19", "min": "2026-05-20"}}]</t>
         </is>
       </c>
       <c r="O201" t="n">
@@ -10262,7 +10262,7 @@
       </c>
       <c r="P201" s="3" t="inlineStr">
         <is>
-          <t>保单到期日在2026-05-19 至 2026-06-19的客户</t>
+          <t>保单到期日在2026-05-20 至 2026-06-19的客户</t>
         </is>
       </c>
       <c r="Q201" t="inlineStr">
@@ -10286,7 +10286,7 @@
         <v>0</v>
       </c>
       <c r="H202" t="n">
-        <v>1411.254999926314</v>
+        <v>1712.975375005044</v>
       </c>
       <c r="J202" t="inlineStr">
         <is>
@@ -10301,7 +10301,7 @@
       </c>
       <c r="N202" s="3" t="inlineStr">
         <is>
-          <t>[{"field": "polNoInfo.claimdatainfo.claimdate", "operator": "RANGE", "value": {"max": "2026-05-19 23:59:59", "min": "2025-05-19 00:00:00"}}]</t>
+          <t>[{"field": "polNoInfo.claimdatainfo.claimdate", "operator": "RANGE", "value": {"max": "2025-12-31 23:59:59", "min": "2025-01-01 00:00:00"}}]</t>
         </is>
       </c>
       <c r="O202" t="n">
@@ -10309,7 +10309,7 @@
       </c>
       <c r="P202" s="3" t="inlineStr">
         <is>
-          <t>理赔时间在2025-05-19 至 2026-05-19的客户</t>
+          <t>理赔时间在2025年的客户</t>
         </is>
       </c>
       <c r="Q202" t="inlineStr">
@@ -10333,7 +10333,7 @@
         <v>0</v>
       </c>
       <c r="H203" t="n">
-        <v>1507.509834016673</v>
+        <v>1460.952166002244</v>
       </c>
       <c r="J203" t="inlineStr">
         <is>
@@ -10380,7 +10380,7 @@
         <v>0</v>
       </c>
       <c r="H204" t="n">
-        <v>1105.12641700916</v>
+        <v>1187.22500000149</v>
       </c>
       <c r="J204" t="inlineStr">
         <is>
@@ -10427,7 +10427,7 @@
         <v>0</v>
       </c>
       <c r="H205" t="n">
-        <v>1306.112249963917</v>
+        <v>1178.038166020997</v>
       </c>
       <c r="J205" t="inlineStr">
         <is>
@@ -10474,7 +10474,7 @@
         <v>0</v>
       </c>
       <c r="H206" t="n">
-        <v>935.9834579518065</v>
+        <v>1335.068249958567</v>
       </c>
       <c r="J206" t="inlineStr">
         <is>
@@ -10521,7 +10521,7 @@
         <v>0</v>
       </c>
       <c r="H207" t="n">
-        <v>1062.499374966137</v>
+        <v>1276.157166925259</v>
       </c>
       <c r="J207" t="inlineStr">
         <is>
@@ -10568,7 +10568,7 @@
         <v>0</v>
       </c>
       <c r="H208" t="n">
-        <v>1000.157332979143</v>
+        <v>1172.490624943748</v>
       </c>
       <c r="J208" t="inlineStr">
         <is>
@@ -10615,7 +10615,7 @@
         <v>0</v>
       </c>
       <c r="H209" t="n">
-        <v>1404.337708023377</v>
+        <v>1199.387667002156</v>
       </c>
       <c r="J209" t="inlineStr">
         <is>
@@ -10662,7 +10662,7 @@
         <v>0</v>
       </c>
       <c r="H210" t="n">
-        <v>1226.780916913413</v>
+        <v>1501.235916977748</v>
       </c>
       <c r="J210" t="inlineStr">
         <is>
@@ -10709,7 +10709,7 @@
         <v>0</v>
       </c>
       <c r="H211" t="n">
-        <v>1404.285874916241</v>
+        <v>1095.885167014785</v>
       </c>
       <c r="J211" t="inlineStr">
         <is>
@@ -10756,7 +10756,7 @@
         <v>0</v>
       </c>
       <c r="H212" t="n">
-        <v>1139.310416998342</v>
+        <v>990.0607080198824</v>
       </c>
       <c r="J212" t="inlineStr">
         <is>
@@ -10803,7 +10803,7 @@
         <v>0</v>
       </c>
       <c r="H213" t="n">
-        <v>1196.557375020348</v>
+        <v>1318.944665952586</v>
       </c>
       <c r="J213" t="inlineStr">
         <is>
@@ -10850,7 +10850,7 @@
         <v>0</v>
       </c>
       <c r="H214" t="n">
-        <v>1132.512665935792</v>
+        <v>1050.924125011079</v>
       </c>
       <c r="J214" t="inlineStr">
         <is>
@@ -10897,7 +10897,7 @@
         <v>0</v>
       </c>
       <c r="H215" t="n">
-        <v>1233.088332926854</v>
+        <v>1073.210708098486</v>
       </c>
       <c r="J215" t="inlineStr">
         <is>
@@ -10945,7 +10945,7 @@
         <v>0</v>
       </c>
       <c r="H216" t="n">
-        <v>1633.21070803795</v>
+        <v>1776.306207990274</v>
       </c>
       <c r="J216" t="inlineStr">
         <is>
@@ -10960,7 +10960,7 @@
       </c>
       <c r="N216" s="3" t="inlineStr">
         <is>
-          <t>[{"field": "familyInfo.familyrelation", "operator": "MATCH", "value": "子女"}, {"field": "familyInfo.familyclientbirthday", "operator": "RANGE", "value": {"max": "2026-05-19 23:59:59", "min": "2008-05-20 00:00:00"}}]</t>
+          <t>[{"field": "familyInfo.familyrelation", "operator": "MATCH", "value": "子女"}, {"field": "familyInfo.familyclientbirthday", "operator": "RANGE", "value": {"max": "2026-05-20 23:59:59", "min": "2008-05-21 00:00:00"}}]</t>
         </is>
       </c>
       <c r="O216" t="n">
@@ -10993,7 +10993,7 @@
         <v>0</v>
       </c>
       <c r="H217" t="n">
-        <v>1602.847333066165</v>
+        <v>1141.953583923168</v>
       </c>
       <c r="J217" t="inlineStr">
         <is>
@@ -11041,7 +11041,7 @@
         <v>0</v>
       </c>
       <c r="H218" t="n">
-        <v>1576.425082981586</v>
+        <v>1162.098082946613</v>
       </c>
       <c r="J218" t="inlineStr">
         <is>
@@ -11089,7 +11089,7 @@
         <v>0</v>
       </c>
       <c r="H219" t="n">
-        <v>4052.516749943607</v>
+        <v>1631.661291001365</v>
       </c>
       <c r="J219" t="inlineStr">
         <is>
@@ -11137,7 +11137,7 @@
         <v>0</v>
       </c>
       <c r="H220" t="n">
-        <v>1363.827207940631</v>
+        <v>1237.403500010259</v>
       </c>
       <c r="J220" t="inlineStr">
         <is>
@@ -11185,7 +11185,7 @@
         <v>0</v>
       </c>
       <c r="H221" t="n">
-        <v>3138.949416927062</v>
+        <v>1821.251875022426</v>
       </c>
       <c r="J221" t="inlineStr">
         <is>
@@ -11234,7 +11234,7 @@
         <v>0</v>
       </c>
       <c r="H222" t="n">
-        <v>1061.517124995589</v>
+        <v>1575.013499939814</v>
       </c>
       <c r="J222" t="inlineStr">
         <is>
@@ -11282,7 +11282,7 @@
         <v>0</v>
       </c>
       <c r="H223" t="n">
-        <v>1535.312875057571</v>
+        <v>1239.836208056659</v>
       </c>
       <c r="J223" t="inlineStr">
         <is>
@@ -11330,7 +11330,7 @@
         <v>0</v>
       </c>
       <c r="H224" t="n">
-        <v>1253.097042092122</v>
+        <v>1495.454207994044</v>
       </c>
       <c r="J224" t="inlineStr">
         <is>
@@ -11378,7 +11378,7 @@
         <v>0</v>
       </c>
       <c r="H225" t="n">
-        <v>1551.626625005156</v>
+        <v>1554.923249990679</v>
       </c>
       <c r="J225" t="inlineStr">
         <is>
@@ -11426,7 +11426,7 @@
         <v>0</v>
       </c>
       <c r="H226" t="n">
-        <v>1259.831750066951</v>
+        <v>1761.679833056405</v>
       </c>
       <c r="J226" t="inlineStr">
         <is>
@@ -11475,7 +11475,7 @@
         <v>0</v>
       </c>
       <c r="H227" t="n">
-        <v>1203.879290958866</v>
+        <v>1181.131124962121</v>
       </c>
       <c r="J227" t="inlineStr">
         <is>
@@ -11523,7 +11523,7 @@
         <v>0</v>
       </c>
       <c r="H228" t="n">
-        <v>1000.330417067744</v>
+        <v>1300.009500002488</v>
       </c>
       <c r="J228" t="inlineStr">
         <is>
@@ -11571,7 +11571,7 @@
         <v>0</v>
       </c>
       <c r="H229" t="n">
-        <v>1332.499707932584</v>
+        <v>1345.371374976821</v>
       </c>
       <c r="J229" t="inlineStr">
         <is>
@@ -11619,7 +11619,7 @@
         <v>0</v>
       </c>
       <c r="H230" t="n">
-        <v>1391.289082937874</v>
+        <v>1307.1982919937</v>
       </c>
       <c r="J230" t="inlineStr">
         <is>
@@ -11634,7 +11634,7 @@
       </c>
       <c r="N230" s="3" t="inlineStr">
         <is>
-          <t>[{"field": "clientAge", "operator": "RANGE", "value": {"max": 55, "min": 45}}, {"field": "annPremSegNum", "operator": "LT", "value": 10000}]</t>
+          <t>[{"field": "clientAge", "operator": "RANGE", "value": {"max": 55, "min": 45}}, {"field": "annPremSegNum", "operator": "LTE", "value": 10000}]</t>
         </is>
       </c>
       <c r="O230" t="n">
@@ -11643,7 +11643,7 @@
       <c r="P230" s="3" t="inlineStr">
         <is>
           <t>客户年龄在45~55之间
-并且年缴保费&lt;10000的客户</t>
+并且年缴保费≤10000的客户</t>
         </is>
       </c>
       <c r="Q230" t="inlineStr">
@@ -11667,7 +11667,7 @@
         <v>0</v>
       </c>
       <c r="H231" t="n">
-        <v>2072.664375067689</v>
+        <v>1722.524417098612</v>
       </c>
       <c r="J231" t="inlineStr">
         <is>
@@ -11716,7 +11716,7 @@
         <v>0</v>
       </c>
       <c r="H232" t="n">
-        <v>1233.019499923103</v>
+        <v>1456.00599993486</v>
       </c>
       <c r="J232" t="inlineStr">
         <is>
@@ -11765,7 +11765,7 @@
         <v>0</v>
       </c>
       <c r="H233" t="n">
-        <v>1744.219249929301</v>
+        <v>1214.357707998715</v>
       </c>
       <c r="J233" t="inlineStr">
         <is>
@@ -11780,7 +11780,7 @@
       </c>
       <c r="N233" s="3" t="inlineStr">
         <is>
-          <t>[{"field": "clientAge", "operator": "GTE", "value": 45}, {"field": "familyInfo.familyrelation", "operator": "MATCH", "value": "父母"}, {"field": "familyInfo.familyclientbirthday", "operator": "LTE", "value": "1956-05-19 23:59:59"}]</t>
+          <t>[{"field": "clientAge", "operator": "GTE", "value": 45}, {"field": "familyInfo.familyclientbirthday", "operator": "LTE", "value": "1956-05-20 23:59:59"}]</t>
         </is>
       </c>
       <c r="O233" t="n">
@@ -11789,8 +11789,7 @@
       <c r="P233" s="3" t="inlineStr">
         <is>
           <t>客户年龄≥45
-并且有父母
-并且父母年龄≥70的客户</t>
+并且家庭成员年龄≥70的客户</t>
         </is>
       </c>
       <c r="Q233" t="inlineStr">
@@ -11814,7 +11813,7 @@
         <v>0</v>
       </c>
       <c r="H234" t="n">
-        <v>1467.216750024818</v>
+        <v>1336.693292018026</v>
       </c>
       <c r="J234" t="inlineStr">
         <is>
@@ -11863,7 +11862,7 @@
         <v>0</v>
       </c>
       <c r="H235" t="n">
-        <v>15.83454199135303</v>
+        <v>17.0275840209797</v>
       </c>
       <c r="J235" t="inlineStr">
         <is>
@@ -11911,7 +11910,7 @@
         <v>0</v>
       </c>
       <c r="H236" t="n">
-        <v>1465.453042066656</v>
+        <v>1394.820375018753</v>
       </c>
       <c r="J236" t="inlineStr">
         <is>
@@ -11959,7 +11958,7 @@
         <v>0</v>
       </c>
       <c r="H237" t="n">
-        <v>1639.339082990773</v>
+        <v>1390.841334010474</v>
       </c>
       <c r="J237" t="inlineStr">
         <is>
@@ -11974,7 +11973,7 @@
       </c>
       <c r="N237" s="3" t="inlineStr">
         <is>
-          <t>[{"field": "familyInfo.familyrelation", "operator": "MATCH", "value": "子女"}, {"field": "familyInfo.familyclientbirthday", "operator": "RANGE", "value": {"max": "2026-05-19 23:59:59", "min": "2008-05-20 00:00:00"}}]</t>
+          <t>[{"field": "familyInfo.familyrelation", "operator": "MATCH", "value": "子女"}, {"field": "familyInfo.familyclientbirthday", "operator": "RANGE", "value": {"max": "2026-05-20 23:59:59", "min": "2008-05-21 00:00:00"}}]</t>
         </is>
       </c>
       <c r="O237" t="n">
@@ -12007,7 +12006,7 @@
         <v>0</v>
       </c>
       <c r="H238" t="n">
-        <v>1365.854167030193</v>
+        <v>1614.193749963306</v>
       </c>
       <c r="J238" t="inlineStr">
         <is>
@@ -12055,7 +12054,7 @@
         <v>0</v>
       </c>
       <c r="H239" t="n">
-        <v>1479.364082915708</v>
+        <v>1327.766709029675</v>
       </c>
       <c r="J239" t="inlineStr">
         <is>
@@ -12103,7 +12102,7 @@
         <v>0</v>
       </c>
       <c r="H240" t="n">
-        <v>29.27133301272988</v>
+        <v>24.9298750422895</v>
       </c>
       <c r="J240" t="inlineStr">
         <is>
@@ -12151,7 +12150,7 @@
         <v>0</v>
       </c>
       <c r="H241" t="n">
-        <v>1448.75945802778</v>
+        <v>2036.4344160771</v>
       </c>
       <c r="J241" t="inlineStr">
         <is>
@@ -12199,7 +12198,7 @@
         <v>0</v>
       </c>
       <c r="H242" t="n">
-        <v>1507.971292012371</v>
+        <v>1605.509583954699</v>
       </c>
       <c r="J242" t="inlineStr">
         <is>
@@ -12214,7 +12213,7 @@
       </c>
       <c r="N242" s="3" t="inlineStr">
         <is>
-          <t>[{"field": "familyInfo.familyrelation", "operator": "MATCH", "value": "子女"}, {"field": "familyInfo.familyclientbirthday", "operator": "RANGE", "value": {"max": "2023-05-19 23:59:59", "min": "2020-05-20 00:00:00"}}]</t>
+          <t>[{"field": "familyInfo.familyrelation", "operator": "MATCH", "value": "子女"}, {"field": "familyInfo.familyclientbirthday", "operator": "RANGE", "value": {"max": "2023-05-20 23:59:59", "min": "2020-05-21 00:00:00"}}]</t>
         </is>
       </c>
       <c r="O242" t="n">
@@ -12247,7 +12246,7 @@
         <v>0</v>
       </c>
       <c r="H243" t="n">
-        <v>11.17137505207211</v>
+        <v>18.49345793016255</v>
       </c>
       <c r="J243" t="inlineStr">
         <is>
@@ -12295,7 +12294,7 @@
         <v>0</v>
       </c>
       <c r="H244" t="n">
-        <v>1148.798250011168</v>
+        <v>1175.878125010058</v>
       </c>
       <c r="J244" t="inlineStr">
         <is>
@@ -12343,7 +12342,7 @@
         <v>0</v>
       </c>
       <c r="H245" t="n">
-        <v>1011.865957989357</v>
+        <v>1184.985207975842</v>
       </c>
       <c r="J245" t="inlineStr">
         <is>
@@ -12391,7 +12390,7 @@
         <v>0</v>
       </c>
       <c r="H246" t="n">
-        <v>1122.44454107713</v>
+        <v>1434.893334051594</v>
       </c>
       <c r="J246" t="inlineStr">
         <is>
@@ -12439,7 +12438,7 @@
         <v>0</v>
       </c>
       <c r="H247" t="n">
-        <v>1070.274999947287</v>
+        <v>1333.232167060487</v>
       </c>
       <c r="J247" t="inlineStr">
         <is>
@@ -12487,7 +12486,7 @@
         <v>0</v>
       </c>
       <c r="H248" t="n">
-        <v>1085.043583996594</v>
+        <v>1444.187083980069</v>
       </c>
       <c r="J248" t="inlineStr">
         <is>
@@ -12535,7 +12534,7 @@
         <v>0</v>
       </c>
       <c r="H249" t="n">
-        <v>1203.049374977127</v>
+        <v>1467.427790979855</v>
       </c>
       <c r="J249" t="inlineStr">
         <is>
@@ -12583,7 +12582,7 @@
         <v>0</v>
       </c>
       <c r="H250" t="n">
-        <v>1251.365375006571</v>
+        <v>1726.931041921489</v>
       </c>
       <c r="J250" t="inlineStr">
         <is>
@@ -12631,7 +12630,7 @@
         <v>0</v>
       </c>
       <c r="H251" t="n">
-        <v>1494.132666965015</v>
+        <v>1609.540208010003</v>
       </c>
       <c r="J251" t="inlineStr">
         <is>
@@ -12680,7 +12679,7 @@
         <v>0</v>
       </c>
       <c r="H252" t="n">
-        <v>1559.451333014295</v>
+        <v>1371.519375010394</v>
       </c>
       <c r="J252" t="inlineStr">
         <is>
@@ -12729,7 +12728,7 @@
         <v>0</v>
       </c>
       <c r="H253" t="n">
-        <v>1988.876209012233</v>
+        <v>1401.809042086825</v>
       </c>
       <c r="J253" t="inlineStr">
         <is>
@@ -12778,7 +12777,7 @@
         <v>0</v>
       </c>
       <c r="H254" t="n">
-        <v>1381.952041992918</v>
+        <v>1799.078207928687</v>
       </c>
       <c r="J254" t="inlineStr">
         <is>
@@ -12827,7 +12826,7 @@
         <v>0</v>
       </c>
       <c r="H255" t="n">
-        <v>1243.382791988552</v>
+        <v>1815.539958071895</v>
       </c>
       <c r="J255" t="inlineStr">
         <is>
@@ -12876,7 +12875,7 @@
         <v>0</v>
       </c>
       <c r="H256" t="n">
-        <v>1305.756125017069</v>
+        <v>1450.442165951245</v>
       </c>
       <c r="J256" t="inlineStr">
         <is>
@@ -12891,7 +12890,7 @@
       </c>
       <c r="N256" s="3" t="inlineStr">
         <is>
-          <t>[{"field": "clientAge", "operator": "GTE", "value": 61}, {"field": "newValueLabel", "operator": "MATCH", "value": "A1"}, {"field": "clientTemperature", "operator": "MATCH", "value": "中温"}]</t>
+          <t>[{"field": "clientAge", "operator": "GTE", "value": 60}, {"field": "newValueLabel", "operator": "MATCH", "value": "A1"}, {"field": "clientTemperature", "operator": "MATCH", "value": "中温"}]</t>
         </is>
       </c>
       <c r="O256" t="n">
@@ -12899,7 +12898,7 @@
       </c>
       <c r="P256" s="3" t="inlineStr">
         <is>
-          <t>客户年龄≥61
+          <t>客户年龄≥60
 并且客户价值标签为A1
 并且客户温度为中温的客户</t>
         </is>
@@ -12925,7 +12924,7 @@
         <v>0</v>
       </c>
       <c r="H257" t="n">
-        <v>1003.974082996137</v>
+        <v>1212.89500000421</v>
       </c>
       <c r="J257" t="inlineStr">
         <is>
@@ -12973,7 +12972,7 @@
         <v>0</v>
       </c>
       <c r="H258" t="n">
-        <v>1616.893874946982</v>
+        <v>1796.879500034265</v>
       </c>
       <c r="J258" t="inlineStr">
         <is>
@@ -13021,7 +13020,7 @@
         <v>0</v>
       </c>
       <c r="H259" t="n">
-        <v>1198.272375040688</v>
+        <v>1224.544374970719</v>
       </c>
       <c r="J259" t="inlineStr">
         <is>
@@ -13069,7 +13068,7 @@
         <v>0</v>
       </c>
       <c r="H260" t="n">
-        <v>1156.773125054315</v>
+        <v>1103.112209006213</v>
       </c>
       <c r="J260" t="inlineStr">
         <is>
@@ -13117,7 +13116,7 @@
         <v>0</v>
       </c>
       <c r="H261" t="n">
-        <v>1290.331042022444</v>
+        <v>1321.513874921948</v>
       </c>
       <c r="J261" t="inlineStr">
         <is>
@@ -13165,7 +13164,7 @@
         <v>0</v>
       </c>
       <c r="H262" t="n">
-        <v>1309.272708953358</v>
+        <v>1215.804624953307</v>
       </c>
       <c r="J262" t="inlineStr">
         <is>
@@ -13213,7 +13212,7 @@
         <v>0</v>
       </c>
       <c r="H263" t="n">
-        <v>1147.88433292415</v>
+        <v>1351.233583991416</v>
       </c>
       <c r="J263" t="inlineStr">
         <is>
@@ -13262,7 +13261,7 @@
         <v>0</v>
       </c>
       <c r="H264" t="n">
-        <v>1301.426624995656</v>
+        <v>1293.284791056067</v>
       </c>
       <c r="J264" t="inlineStr">
         <is>
@@ -13310,7 +13309,7 @@
         <v>0</v>
       </c>
       <c r="H265" t="n">
-        <v>1646.399541990831</v>
+        <v>1453.302333015017</v>
       </c>
       <c r="J265" t="inlineStr">
         <is>
@@ -13325,7 +13324,7 @@
       </c>
       <c r="N265" s="3" t="inlineStr">
         <is>
-          <t>[{"field": "newValueLabel", "operator": "MATCH", "value": "A1"}, {"field": "effAppEndDate", "operator": "RANGE", "value": {"max": "2026-05-19", "min": "2021-05-19"}}]</t>
+          <t>[{"field": "newValueLabel", "operator": "MATCH", "value": "A1"}, {"field": "effAppEndDate", "operator": "RANGE", "value": {"max": "2026-05-20", "min": "2021-05-20"}}]</t>
         </is>
       </c>
       <c r="O265" t="n">
@@ -13334,7 +13333,7 @@
       <c r="P265" s="3" t="inlineStr">
         <is>
           <t>客户价值标签为A1
-并且缴费期满日在2021-05-19 至 2026-05-19的客户</t>
+并且缴费期满日在2021-05-20 至 2026-05-20的客户</t>
         </is>
       </c>
       <c r="Q265" t="inlineStr">
@@ -13358,7 +13357,7 @@
         <v>0</v>
       </c>
       <c r="H266" t="n">
-        <v>1643.561541917734</v>
+        <v>1547.90258302819</v>
       </c>
       <c r="J266" t="inlineStr">
         <is>
@@ -13373,7 +13372,7 @@
       </c>
       <c r="N266" s="3" t="inlineStr">
         <is>
-          <t>[{"field": "newValueLabel", "operator": "MATCH", "value": "A1"}, {"field": "familyInfo.familyrelation", "operator": "MATCH", "value": "子女"}, {"field": "familyInfo.familyclientbirthday", "operator": "RANGE", "value": {"max": "2026-05-19 23:59:59", "min": "2008-05-20 00:00:00"}}]</t>
+          <t>[{"field": "newValueLabel", "operator": "MATCH", "value": "A1"}, {"field": "familyInfo.familyrelation", "operator": "MATCH", "value": "子女"}, {"field": "familyInfo.familyclientbirthday", "operator": "RANGE", "value": {"max": "2026-05-20 23:59:59", "min": "2008-05-21 00:00:00"}}]</t>
         </is>
       </c>
       <c r="O266" t="n">
@@ -13407,7 +13406,7 @@
         <v>0</v>
       </c>
       <c r="H267" t="n">
-        <v>1864.791083033197</v>
+        <v>1768.959957989864</v>
       </c>
       <c r="J267" t="inlineStr">
         <is>
@@ -13455,7 +13454,7 @@
         <v>0</v>
       </c>
       <c r="H268" t="n">
-        <v>1136.307875043713</v>
+        <v>1477.484583039768</v>
       </c>
       <c r="J268" t="inlineStr">
         <is>
@@ -13503,7 +13502,7 @@
         <v>0</v>
       </c>
       <c r="H269" t="n">
-        <v>1842.451250064187</v>
+        <v>1610.329584102146</v>
       </c>
       <c r="J269" t="inlineStr">
         <is>
@@ -13551,7 +13550,7 @@
         <v>0</v>
       </c>
       <c r="H270" t="n">
-        <v>1265.551707940176</v>
+        <v>1553.155875066295</v>
       </c>
       <c r="J270" t="inlineStr">
         <is>
@@ -13601,7 +13600,7 @@
         <v>0</v>
       </c>
       <c r="H271" t="n">
-        <v>997.2586669027805</v>
+        <v>1698.730207979679</v>
       </c>
       <c r="J271" t="inlineStr">
         <is>
@@ -13649,7 +13648,7 @@
         <v>0</v>
       </c>
       <c r="H272" t="n">
-        <v>1073.948708013631</v>
+        <v>1208.159833913669</v>
       </c>
       <c r="J272" t="inlineStr">
         <is>
@@ -13697,7 +13696,7 @@
         <v>0</v>
       </c>
       <c r="H273" t="n">
-        <v>1233.917083009146</v>
+        <v>1479.636874981225</v>
       </c>
       <c r="J273" t="inlineStr">
         <is>
@@ -13745,7 +13744,7 @@
         <v>0</v>
       </c>
       <c r="H274" t="n">
-        <v>1307.054583099671</v>
+        <v>1184.027332928963</v>
       </c>
       <c r="J274" t="inlineStr">
         <is>
@@ -13793,7 +13792,7 @@
         <v>0</v>
       </c>
       <c r="H275" t="n">
-        <v>1199.874290963635</v>
+        <v>1097.12358401157</v>
       </c>
       <c r="J275" t="inlineStr">
         <is>
@@ -13841,7 +13840,7 @@
         <v>0</v>
       </c>
       <c r="H276" t="n">
-        <v>1211.466624983586</v>
+        <v>1605.461333994754</v>
       </c>
       <c r="J276" t="inlineStr">
         <is>
@@ -13889,7 +13888,7 @@
         <v>0</v>
       </c>
       <c r="H277" t="n">
-        <v>1168.278874945827</v>
+        <v>1283.873582957312</v>
       </c>
       <c r="J277" t="inlineStr">
         <is>
@@ -13937,7 +13936,7 @@
         <v>0</v>
       </c>
       <c r="H278" t="n">
-        <v>1019.240082940087</v>
+        <v>1067.970709060319</v>
       </c>
       <c r="J278" t="inlineStr">
         <is>
@@ -13985,7 +13984,7 @@
         <v>0</v>
       </c>
       <c r="H279" t="n">
-        <v>1186.482082935981</v>
+        <v>1334.408832946792</v>
       </c>
       <c r="J279" t="inlineStr">
         <is>
@@ -14033,7 +14032,7 @@
         <v>0</v>
       </c>
       <c r="H280" t="n">
-        <v>1164.950291975401</v>
+        <v>1216.834749910049</v>
       </c>
       <c r="J280" t="inlineStr">
         <is>
@@ -14081,7 +14080,7 @@
         <v>0</v>
       </c>
       <c r="H281" t="n">
-        <v>1647.024124977179</v>
+        <v>1436.418832978234</v>
       </c>
       <c r="J281" t="inlineStr">
         <is>
@@ -14129,7 +14128,7 @@
         <v>0</v>
       </c>
       <c r="H282" t="n">
-        <v>1495.26291701477</v>
+        <v>1440.654958947562</v>
       </c>
       <c r="J282" t="inlineStr">
         <is>
@@ -14176,7 +14175,7 @@
         <v>0</v>
       </c>
       <c r="H283" t="n">
-        <v>1805.695166927762</v>
+        <v>1461.194667033851</v>
       </c>
       <c r="J283" t="inlineStr">
         <is>
@@ -14224,7 +14223,7 @@
         <v>0</v>
       </c>
       <c r="H284" t="n">
-        <v>1304.417042061687</v>
+        <v>1342.685291892849</v>
       </c>
       <c r="J284" t="inlineStr">
         <is>
@@ -14239,7 +14238,7 @@
       </c>
       <c r="N284" s="3" t="inlineStr">
         <is>
-          <t>[{"field": "idValidDate", "operator": "RANGE", "value": {"max": "2026-06-19 00:00:00", "min": "2026-05-20 00:00:00"}}]</t>
+          <t>[{"field": "idValidDate", "operator": "RANGE", "value": {"max": "2026-06-20 00:00:00", "min": "2026-05-21 00:00:00"}}]</t>
         </is>
       </c>
       <c r="O284" t="n">
@@ -14247,7 +14246,7 @@
       </c>
       <c r="P284" s="3" t="inlineStr">
         <is>
-          <t>证件有效期在2026-05-20 至 2026-06-19的客户</t>
+          <t>证件有效期在2026-05-21 至 2026-06-20的客户</t>
         </is>
       </c>
       <c r="Q284" t="inlineStr">
@@ -14271,7 +14270,7 @@
         <v>0</v>
       </c>
       <c r="H285" t="n">
-        <v>1230.97679100465</v>
+        <v>1543.991208076477</v>
       </c>
       <c r="J285" t="inlineStr">
         <is>
@@ -14318,7 +14317,7 @@
         <v>0</v>
       </c>
       <c r="H286" t="n">
-        <v>1465.992750017904</v>
+        <v>1605.363499955274</v>
       </c>
       <c r="J286" t="inlineStr">
         <is>
@@ -14366,7 +14365,7 @@
         <v>0</v>
       </c>
       <c r="H287" t="n">
-        <v>1557.352792005986</v>
+        <v>1962.76579098776</v>
       </c>
       <c r="J287" t="inlineStr">
         <is>
@@ -14416,7 +14415,7 @@
         <v>0</v>
       </c>
       <c r="H288" t="n">
-        <v>1095.225083059631</v>
+        <v>1620.741166989319</v>
       </c>
       <c r="J288" t="inlineStr">
         <is>
@@ -14431,7 +14430,7 @@
       </c>
       <c r="N288" s="3" t="inlineStr">
         <is>
-          <t>[{"field": "clientAge", "operator": "GTE", "value": 45}, {"field": "familyInfo.familyclientbirthday", "operator": "LTE", "value": "1971-05-19 23:59:59"}, {"field": "isBuyPension", "operator": "MATCH", "value": "有购买"}]</t>
+          <t>[{"field": "clientAge", "operator": "GTE", "value": 45}, {"field": "familyInfo.familyclientbirthday", "operator": "LTE", "value": "1971-05-20 23:59:59"}, {"field": "isBuyPension", "operator": "MATCH", "value": "有购买"}]</t>
         </is>
       </c>
       <c r="O288" t="n">
@@ -14465,7 +14464,7 @@
         <v>0</v>
       </c>
       <c r="H289" t="n">
-        <v>1532.167208963074</v>
+        <v>1669.404583983123</v>
       </c>
       <c r="J289" t="inlineStr">
         <is>
@@ -14515,7 +14514,7 @@
         <v>0</v>
       </c>
       <c r="H290" t="n">
-        <v>1473.179291002452</v>
+        <v>1653.768457937986</v>
       </c>
       <c r="J290" t="inlineStr">
         <is>
@@ -14564,7 +14563,7 @@
         <v>0</v>
       </c>
       <c r="H291" t="n">
-        <v>1257.581999991089</v>
+        <v>2810.251666931435</v>
       </c>
       <c r="J291" t="inlineStr">
         <is>
@@ -14613,7 +14612,7 @@
         <v>0</v>
       </c>
       <c r="H292" t="n">
-        <v>1432.171540916897</v>
+        <v>1816.518209059723</v>
       </c>
       <c r="J292" t="inlineStr">
         <is>
@@ -14662,7 +14661,7 @@
         <v>0</v>
       </c>
       <c r="H293" t="n">
-        <v>1095.165250007994</v>
+        <v>1730.896958964877</v>
       </c>
       <c r="J293" t="inlineStr">
         <is>
@@ -14677,7 +14676,7 @@
       </c>
       <c r="N293" s="3" t="inlineStr">
         <is>
-          <t>[{"field": "clientAge", "operator": "GTE", "value": 45}, {"field": "familyInfo.familyclientbirthday", "operator": "LTE", "value": "1971-05-19 23:59:59"}, {"field": "pCategorys", "operator": "NOT_CONTAINS", "value": ["医疗保险"]}]</t>
+          <t>[{"field": "clientAge", "operator": "GTE", "value": 45}, {"field": "familyInfo.familyclientbirthday", "operator": "LTE", "value": "1971-05-20 23:59:59"}, {"field": "pCategorys", "operator": "NOT_CONTAINS", "value": ["医疗保险"]}]</t>
         </is>
       </c>
       <c r="O293" t="n">
@@ -14711,7 +14710,7 @@
         <v>0</v>
       </c>
       <c r="H294" t="n">
-        <v>1239.721874939278</v>
+        <v>1918.87754201889</v>
       </c>
       <c r="J294" t="inlineStr">
         <is>
@@ -14760,7 +14759,7 @@
         <v>0</v>
       </c>
       <c r="H295" t="n">
-        <v>1330.747124971822</v>
+        <v>1981.239999993704</v>
       </c>
       <c r="J295" t="inlineStr">
         <is>
@@ -14810,7 +14809,7 @@
         <v>0</v>
       </c>
       <c r="H296" t="n">
-        <v>1017.28266698774</v>
+        <v>1528.232124983333</v>
       </c>
       <c r="J296" t="inlineStr">
         <is>
@@ -14859,7 +14858,7 @@
         <v>0</v>
       </c>
       <c r="H297" t="n">
-        <v>1692.538209026679</v>
+        <v>1528.792000026442</v>
       </c>
       <c r="J297" t="inlineStr">
         <is>
@@ -14908,7 +14907,7 @@
         <v>0</v>
       </c>
       <c r="H298" t="n">
-        <v>1394.864709000103</v>
+        <v>2170.426915981807</v>
       </c>
       <c r="J298" t="inlineStr">
         <is>
@@ -14958,7 +14957,7 @@
         <v>0</v>
       </c>
       <c r="H299" t="n">
-        <v>1256.04216591455</v>
+        <v>1745.051375008188</v>
       </c>
       <c r="J299" t="inlineStr">
         <is>
@@ -14973,7 +14972,7 @@
       </c>
       <c r="N299" s="3" t="inlineStr">
         <is>
-          <t>[{"field": "familyInfo.familyrelation", "operator": "MATCH", "value": "(外)孙子女"}, {"field": "familyInfo.familyclientbirthday", "operator": "LTE", "value": "1971-05-19 23:59:59"}, {"field": "isBuyPension", "operator": "MATCH", "value": "有购买"}]</t>
+          <t>[{"field": "familyInfo.familyrelation", "operator": "MATCH", "value": "(外)孙子女"}, {"field": "familyInfo.familyclientbirthday", "operator": "LTE", "value": "1971-05-20 23:59:59"}, {"field": "isBuyPension", "operator": "MATCH", "value": "有购买"}]</t>
         </is>
       </c>
       <c r="O299" t="n">
@@ -15007,7 +15006,7 @@
         <v>0</v>
       </c>
       <c r="H300" t="n">
-        <v>1736.947875004262</v>
+        <v>1238.261541933753</v>
       </c>
       <c r="J300" t="inlineStr">
         <is>
@@ -15022,7 +15021,7 @@
       </c>
       <c r="N300" s="3" t="inlineStr">
         <is>
-          <t>[{"field": "clientAge", "operator": "GTE", "value": 40}, {"field": "familyInfo.familyclientbirthday", "operator": "LTE", "value": "1971-05-19 23:59:59"}, {"field": "pCategorys", "operator": "MATCH", "value": "疾病保险"}]</t>
+          <t>[{"field": "clientAge", "operator": "GTE", "value": 40}, {"field": "familyInfo.familyclientbirthday", "operator": "LTE", "value": "1971-05-20 23:59:59"}, {"field": "pCategorys", "operator": "MATCH", "value": "疾病保险"}]</t>
         </is>
       </c>
       <c r="O300" t="n">
@@ -15056,7 +15055,7 @@
         <v>0</v>
       </c>
       <c r="H301" t="n">
-        <v>1775.130624999292</v>
+        <v>1693.008375004865</v>
       </c>
       <c r="J301" t="inlineStr">
         <is>
@@ -15071,7 +15070,7 @@
       </c>
       <c r="N301" s="3" t="inlineStr">
         <is>
-          <t>[{"field": "familyInfo.familyrelation", "operator": "MATCH", "value": "(外)孙子女"}, {"field": "familyInfo.familyclientbirthday", "operator": "GTE", "value": "1965-05-20 00:00:00"}, {"field": "polNoInfo.plancodeinfo.plantypedesc", "operator": "MATCH", "value": "年金"}, {"field": "mariSts", "operator": "MATCH", "value": "已婚"}]</t>
+          <t>[{"field": "clientAge", "operator": "LTE", "value": 60}, {"field": "mariSts", "operator": "MATCH", "value": "已婚"}, {"field": "familyInfo.familyrelation", "operator": "MATCH", "value": "(外)孙子女"}, {"field": "polNoInfo.plancodeinfo.plantypedesc", "operator": "MATCH", "value": "年金"}]</t>
         </is>
       </c>
       <c r="O301" t="n">
@@ -15079,10 +15078,10 @@
       </c>
       <c r="P301" s="3" t="inlineStr">
         <is>
-          <t>有(外)孙子女
-并且(外)孙子女年龄≤60
-并且投保险种类别为年金
-并且客户婚姻状况为已婚的客户</t>
+          <t>客户年龄≤60
+并且客户婚姻状况为已婚
+并且有(外)孙子女
+并且投保险种类别为年金的客户</t>
         </is>
       </c>
       <c r="Q301" t="inlineStr">
@@ -15106,7 +15105,7 @@
         <v>0</v>
       </c>
       <c r="H302" t="n">
-        <v>1135.660249972716</v>
+        <v>1635.04041696433</v>
       </c>
       <c r="J302" t="inlineStr">
         <is>
@@ -15121,7 +15120,7 @@
       </c>
       <c r="N302" s="3" t="inlineStr">
         <is>
-          <t>[{"field": "clientAge", "operator": "GTE", "value": 50}, {"field": "familyInfo.familyclientbirthday", "operator": "LTE", "value": "1971-05-19 23:59:59"}, {"field": "polNoInfo.plancodeinfo.abbrname", "operator": "MATCH", "value": "e生保"}]</t>
+          <t>[{"field": "clientAge", "operator": "GTE", "value": 50}, {"field": "familyInfo.familyclientbirthday", "operator": "LTE", "value": "1971-05-20 23:59:59"}, {"field": "polNoInfo.plancodeinfo.abbrname", "operator": "MATCH", "value": "e生保"}]</t>
         </is>
       </c>
       <c r="O302" t="n">
@@ -15155,7 +15154,7 @@
         <v>0</v>
       </c>
       <c r="H303" t="n">
-        <v>1521.042042062618</v>
+        <v>1519.633332965896</v>
       </c>
       <c r="J303" t="inlineStr">
         <is>
@@ -15205,7 +15204,7 @@
         <v>0</v>
       </c>
       <c r="H304" t="n">
-        <v>1117.6300420193</v>
+        <v>1301.272833021358</v>
       </c>
       <c r="J304" t="inlineStr">
         <is>
@@ -15220,7 +15219,7 @@
       </c>
       <c r="N304" s="3" t="inlineStr">
         <is>
-          <t>[{"field": "clientAge", "operator": "GTE", "value": 40}, {"field": "familyInfo.familyclientbirthday", "operator": "LTE", "value": "1971-05-19 23:59:59"}, {"field": "pCategorys", "operator": "MATCH", "value": "意外伤害保险"}]</t>
+          <t>[{"field": "clientAge", "operator": "GTE", "value": 40}, {"field": "familyInfo.familyclientbirthday", "operator": "LTE", "value": "1971-05-20 23:59:59"}, {"field": "pCategorys", "operator": "MATCH", "value": "意外伤害保险"}]</t>
         </is>
       </c>
       <c r="O304" t="n">
@@ -15254,7 +15253,7 @@
         <v>0</v>
       </c>
       <c r="H305" t="n">
-        <v>1791.71620903071</v>
+        <v>1409.999707946554</v>
       </c>
       <c r="J305" t="inlineStr">
         <is>
@@ -15303,7 +15302,7 @@
         <v>0</v>
       </c>
       <c r="H306" t="n">
-        <v>1334.805458085611</v>
+        <v>1714.325874927454</v>
       </c>
       <c r="J306" t="inlineStr">
         <is>
@@ -15352,7 +15351,7 @@
         <v>0</v>
       </c>
       <c r="H307" t="n">
-        <v>1710.508416988887</v>
+        <v>1833.019042038359</v>
       </c>
       <c r="J307" t="inlineStr">
         <is>
@@ -15401,7 +15400,7 @@
         <v>0</v>
       </c>
       <c r="H308" t="n">
-        <v>1294.989624992013</v>
+        <v>1299.960874952376</v>
       </c>
       <c r="J308" t="inlineStr">
         <is>
@@ -15450,7 +15449,7 @@
         <v>0</v>
       </c>
       <c r="H309" t="n">
-        <v>1595.425290986896</v>
+        <v>1286.87033301685</v>
       </c>
       <c r="J309" t="inlineStr">
         <is>
@@ -15499,7 +15498,7 @@
         <v>0</v>
       </c>
       <c r="H310" t="n">
-        <v>1373.10399999842</v>
+        <v>1456.3695830293</v>
       </c>
       <c r="J310" t="inlineStr">
         <is>
@@ -15548,7 +15547,7 @@
         <v>0</v>
       </c>
       <c r="H311" t="n">
-        <v>1212.504916940816</v>
+        <v>1316.170166945085</v>
       </c>
       <c r="J311" t="inlineStr">
         <is>
@@ -15597,7 +15596,7 @@
         <v>0</v>
       </c>
       <c r="H312" t="n">
-        <v>1479.420040966943</v>
+        <v>1234.267875086516</v>
       </c>
       <c r="J312" t="inlineStr">
         <is>
@@ -15612,7 +15611,7 @@
       </c>
       <c r="N312" s="3" t="inlineStr">
         <is>
-          <t>[{"field": "clientAge", "operator": "GTE", "value": 61}, {"field": "newValueLabel", "operator": "MATCH", "value": "A1"}, {"field": "planAbbrNames", "operator": "EXISTS", "value": ""}]</t>
+          <t>[{"field": "clientAge", "operator": "GTE", "value": 60}, {"field": "newValueLabel", "operator": "MATCH", "value": "A1"}, {"field": "planAbbrNames", "operator": "EXISTS", "value": ""}]</t>
         </is>
       </c>
       <c r="O312" t="n">
@@ -15620,7 +15619,7 @@
       </c>
       <c r="P312" s="3" t="inlineStr">
         <is>
-          <t>客户年龄≥61
+          <t>客户年龄≥60
 并且客户价值标签为A1
 并且有寿险产品的客户</t>
         </is>
@@ -15646,7 +15645,7 @@
         <v>0</v>
       </c>
       <c r="H313" t="n">
-        <v>1502.154125017114</v>
+        <v>1343.405208084732</v>
       </c>
       <c r="J313" t="inlineStr">
         <is>
@@ -15695,7 +15694,7 @@
         <v>0</v>
       </c>
       <c r="H314" t="n">
-        <v>1088.181208004244</v>
+        <v>1377.053375006653</v>
       </c>
       <c r="J314" t="inlineStr">
         <is>
@@ -15744,7 +15743,7 @@
         <v>0</v>
       </c>
       <c r="H315" t="n">
-        <v>1129.135334049352</v>
+        <v>1555.017667007633</v>
       </c>
       <c r="J315" t="inlineStr">
         <is>
@@ -15793,7 +15792,7 @@
         <v>0</v>
       </c>
       <c r="H316" t="n">
-        <v>1372.813625028357</v>
+        <v>1526.655792025849</v>
       </c>
       <c r="J316" t="inlineStr">
         <is>
@@ -15842,7 +15841,7 @@
         <v>0</v>
       </c>
       <c r="H317" t="n">
-        <v>1402.714208932593</v>
+        <v>1709.842125070281</v>
       </c>
       <c r="J317" t="inlineStr">
         <is>
@@ -15891,7 +15890,7 @@
         <v>0</v>
       </c>
       <c r="H318" t="n">
-        <v>1144.05354205519</v>
+        <v>1846.492624958046</v>
       </c>
       <c r="J318" t="inlineStr">
         <is>
@@ -15941,7 +15940,7 @@
         <v>0</v>
       </c>
       <c r="H319" t="n">
-        <v>1318.943666992709</v>
+        <v>1785.034208092839</v>
       </c>
       <c r="J319" t="inlineStr">
         <is>
@@ -15990,7 +15989,7 @@
         <v>0</v>
       </c>
       <c r="H320" t="n">
-        <v>1970.534499967471</v>
+        <v>2160.594125045463</v>
       </c>
       <c r="J320" t="inlineStr">
         <is>
@@ -16005,7 +16004,7 @@
       </c>
       <c r="N320" s="3" t="inlineStr">
         <is>
-          <t>[{"field": "newValueLabel", "operator": "MATCH", "value": "A1"}, {"field": "clientTemperature", "operator": "MATCH", "value": "高温"}, {"field": "familyInfo.familyrelation", "operator": "MATCH", "value": "子女"}, {"field": "familyInfo.familyclientbirthday", "operator": "RANGE", "value": {"max": "2026-05-19 23:59:59", "min": "2008-05-20 00:00:00"}}, {"field": "polNoInfo.plancodeinfo.abbrname", "operator": "MATCH", "value": "e生保"}]</t>
+          <t>[{"field": "newValueLabel", "operator": "MATCH", "value": "A1"}, {"field": "clientTemperature", "operator": "MATCH", "value": "高温"}, {"field": "familyInfo.familyrelation", "operator": "MATCH", "value": "子女"}, {"field": "familyInfo.familyclientbirthday", "operator": "RANGE", "value": {"max": "2026-05-20 23:59:59", "min": "2008-05-21 00:00:00"}}, {"field": "polNoInfo.plancodeinfo.abbrname", "operator": "MATCH", "value": "e生保"}]</t>
         </is>
       </c>
       <c r="O320" t="n">
@@ -16041,7 +16040,7 @@
         <v>0</v>
       </c>
       <c r="H321" t="n">
-        <v>1588.517625001259</v>
+        <v>1596.579916891642</v>
       </c>
       <c r="J321" t="inlineStr">
         <is>
@@ -16091,7 +16090,7 @@
         <v>0</v>
       </c>
       <c r="H322" t="n">
-        <v>1524.076667032205</v>
+        <v>1841.261291992851</v>
       </c>
       <c r="J322" t="inlineStr">
         <is>
@@ -16141,7 +16140,7 @@
         <v>0</v>
       </c>
       <c r="H323" t="n">
-        <v>1321.339875110425</v>
+        <v>1936.259582987987</v>
       </c>
       <c r="J323" t="inlineStr">
         <is>
@@ -16191,7 +16190,7 @@
         <v>0</v>
       </c>
       <c r="H324" t="n">
-        <v>1800.710792071186</v>
+        <v>1821.826792089269</v>
       </c>
       <c r="J324" t="inlineStr">
         <is>
@@ -16241,7 +16240,7 @@
         <v>0</v>
       </c>
       <c r="H325" t="n">
-        <v>1390.751332975924</v>
+        <v>1729.904042091221</v>
       </c>
       <c r="J325" t="inlineStr">
         <is>
@@ -16291,7 +16290,7 @@
         <v>0</v>
       </c>
       <c r="H326" t="n">
-        <v>1660.849500098266</v>
+        <v>1534.935500007123</v>
       </c>
       <c r="J326" t="inlineStr">
         <is>
@@ -16306,7 +16305,7 @@
       </c>
       <c r="N326" s="3" t="inlineStr">
         <is>
-          <t>[{"field": "clientTemperature", "operator": "MATCH", "value": "中温"}, {"field": "newValueLabel", "operator": "MATCH", "value": "B"}, {"field": "isBuyPension", "operator": "MATCH", "value": "有购买"}, {"field": "familyInfo.familyclientbirthday", "operator": "LTE", "value": "1971-05-19 23:59:59"}]</t>
+          <t>[{"field": "clientTemperature", "operator": "MATCH", "value": "中温"}, {"field": "newValueLabel", "operator": "MATCH", "value": "B"}, {"field": "isBuyPension", "operator": "MATCH", "value": "有购买"}, {"field": "familyInfo.familyclientbirthday", "operator": "LTE", "value": "1971-05-20 23:59:59"}]</t>
         </is>
       </c>
       <c r="O326" t="n">
@@ -16341,7 +16340,7 @@
         <v>0</v>
       </c>
       <c r="H327" t="n">
-        <v>1771.903416956775</v>
+        <v>1673.071458004415</v>
       </c>
       <c r="J327" t="inlineStr">
         <is>
@@ -16391,7 +16390,7 @@
         <v>0</v>
       </c>
       <c r="H328" t="n">
-        <v>1599.476292030886</v>
+        <v>1800.413249991834</v>
       </c>
       <c r="J328" t="inlineStr">
         <is>
@@ -16406,7 +16405,7 @@
       </c>
       <c r="N328" s="3" t="inlineStr">
         <is>
-          <t>[{"field": "clientTemperature", "operator": "MATCH", "value": "高温"}, {"field": "newValueLabel", "operator": "MATCH", "value": "A1"}, {"field": "pCategorys", "operator": "MATCH", "value": "疾病保险"}, {"field": "familyInfo.familyrelation", "operator": "MATCH", "value": "子女"}, {"field": "familyInfo.familyclientbirthday", "operator": "RANGE", "value": {"max": "2026-05-19 23:59:59", "min": "2008-05-20 00:00:00"}}]</t>
+          <t>[{"field": "clientTemperature", "operator": "MATCH", "value": "高温"}, {"field": "newValueLabel", "operator": "MATCH", "value": "A1"}, {"field": "pCategorys", "operator": "MATCH", "value": "疾病保险"}, {"field": "familyInfo.familyrelation", "operator": "MATCH", "value": "子女"}, {"field": "familyInfo.familyclientbirthday", "operator": "RANGE", "value": {"max": "2026-05-20 23:59:59", "min": "2008-05-21 00:00:00"}}]</t>
         </is>
       </c>
       <c r="O328" t="n">
@@ -16442,7 +16441,7 @@
         <v>0</v>
       </c>
       <c r="H329" t="n">
-        <v>1260.743417078629</v>
+        <v>1397.97104196623</v>
       </c>
       <c r="J329" t="inlineStr">
         <is>
@@ -16492,7 +16491,7 @@
         <v>0</v>
       </c>
       <c r="H330" t="n">
-        <v>1296.082416083664</v>
+        <v>2139.359334018081</v>
       </c>
       <c r="J330" t="inlineStr">
         <is>
@@ -16507,7 +16506,7 @@
       </c>
       <c r="N330" s="3" t="inlineStr">
         <is>
-          <t>[{"field": "newValueLabel", "operator": "MATCH", "value": "B"}, {"field": "clientTemperature", "operator": "MATCH", "value": "中温"}, {"field": "isBuyPension", "operator": "MATCH", "value": "有购买"}, {"field": "assetsCondition", "operator": "CONTAINS", "value": ["有房", "有房有车"]}]</t>
+          <t>[{"field": "newValueLabel", "operator": "MATCH", "value": "B"}, {"field": "clientTemperature", "operator": "MATCH", "value": "中温"}, {"field": "isBuyPension", "operator": "MATCH", "value": "有购买"}, {"field": "assetsCondition", "operator": "CONTAINS", "value": ["有车", "有房有车"]}]</t>
         </is>
       </c>
       <c r="O330" t="n">
@@ -16518,7 +16517,7 @@
           <t>客户价值标签为B
 并且客户温度为中温
 并且是养老险客户
-并且客户资产状况包含有房、有房有车的客户</t>
+并且客户资产状况包含有车、有房有车的客户</t>
         </is>
       </c>
       <c r="Q330" t="inlineStr">
@@ -16542,7 +16541,7 @@
         <v>0</v>
       </c>
       <c r="H331" t="n">
-        <v>1234.915500041097</v>
+        <v>1670.020540943369</v>
       </c>
       <c r="J331" t="inlineStr">
         <is>
@@ -16592,7 +16591,7 @@
         <v>0</v>
       </c>
       <c r="H332" t="n">
-        <v>1408.150583039969</v>
+        <v>1465.566041064449</v>
       </c>
       <c r="J332" t="inlineStr">
         <is>
@@ -16641,7 +16640,7 @@
         <v>0</v>
       </c>
       <c r="H333" t="n">
-        <v>1349.191500106826</v>
+        <v>1272.389833000489</v>
       </c>
       <c r="J333" t="inlineStr">
         <is>
@@ -16690,7 +16689,7 @@
         <v>0</v>
       </c>
       <c r="H334" t="n">
-        <v>1198.159084073268</v>
+        <v>1545.857249991968</v>
       </c>
       <c r="J334" t="inlineStr">
         <is>
@@ -16739,7 +16738,7 @@
         <v>0</v>
       </c>
       <c r="H335" t="n">
-        <v>1388.276625075378</v>
+        <v>1546.19279189501</v>
       </c>
       <c r="J335" t="inlineStr">
         <is>
@@ -16788,7 +16787,7 @@
         <v>0</v>
       </c>
       <c r="H336" t="n">
-        <v>1536.277708946727</v>
+        <v>2094.1739580594</v>
       </c>
       <c r="J336" t="inlineStr">
         <is>
@@ -16837,7 +16836,7 @@
         <v>0</v>
       </c>
       <c r="H337" t="n">
-        <v>1252.484083990566</v>
+        <v>1658.376459032297</v>
       </c>
       <c r="J337" t="inlineStr">
         <is>
@@ -16886,7 +16885,7 @@
         <v>0</v>
       </c>
       <c r="H338" t="n">
-        <v>1607.161250081845</v>
+        <v>2083.097290946171</v>
       </c>
       <c r="J338" t="inlineStr">
         <is>
@@ -16936,7 +16935,7 @@
         <v>0</v>
       </c>
       <c r="H339" t="n">
-        <v>1923.268917016685</v>
+        <v>1531.959625077434</v>
       </c>
       <c r="J339" t="inlineStr">
         <is>
@@ -16986,7 +16985,7 @@
         <v>0</v>
       </c>
       <c r="H340" t="n">
-        <v>1599.415333010256</v>
+        <v>1820.87620801758</v>
       </c>
       <c r="J340" t="inlineStr">
         <is>
@@ -17035,7 +17034,7 @@
         <v>0</v>
       </c>
       <c r="H341" t="n">
-        <v>1464.946208987385</v>
+        <v>1524.594166898169</v>
       </c>
       <c r="J341" t="inlineStr">
         <is>
@@ -17050,7 +17049,7 @@
       </c>
       <c r="N341" s="3" t="inlineStr">
         <is>
-          <t>[{"field": "clientTemperature", "operator": "MATCH", "value": "高温"}, {"field": "newValueLabel", "operator": "MATCH", "value": "B"}, {"field": "familyInfo.familyclientbirthday", "operator": "LTE", "value": "1971-05-19 23:59:59"}, {"field": "polNoInfo.polStatus", "operator": "MATCH", "value": "等待续保"}]</t>
+          <t>[{"field": "clientTemperature", "operator": "MATCH", "value": "高温"}, {"field": "newValueLabel", "operator": "MATCH", "value": "B"}, {"field": "familyInfo.familyclientbirthday", "operator": "LTE", "value": "1971-05-20 23:59:59"}, {"field": "polNoInfo.polStatus", "operator": "MATCH", "value": "等待续保"}]</t>
         </is>
       </c>
       <c r="O341" t="n">
@@ -17085,7 +17084,7 @@
         <v>0</v>
       </c>
       <c r="H342" t="n">
-        <v>1837.330665905029</v>
+        <v>2202.620333060622</v>
       </c>
       <c r="J342" t="inlineStr">
         <is>
@@ -17136,7 +17135,7 @@
         <v>0</v>
       </c>
       <c r="H343" t="n">
-        <v>1720.463167061098</v>
+        <v>1924.235792015679</v>
       </c>
       <c r="J343" t="inlineStr">
         <is>
@@ -17151,7 +17150,7 @@
       </c>
       <c r="N343" s="3" t="inlineStr">
         <is>
-          <t>[{"field": "newValueLabel", "operator": "MATCH", "value": "B"}, {"field": "clientTemperature", "operator": "MATCH", "value": "低温"}, {"field": "familyInfo.familyrelation", "operator": "MATCH", "value": "子女"}, {"field": "polNoInfo.polStatus", "operator": "MATCH", "value": "交费有效"}]</t>
+          <t>[{"field": "newValueLabel", "operator": "MATCH", "value": "B"}, {"field": "clientTemperature", "operator": "MATCH", "value": "低温"}, {"field": "familyInfo.familyrelation", "operator": "MATCH", "value": "子女"}, {"field": "polNoInfo.polStatus", "operator": "CONTAINS", "value": ["交费有效", "自垫交清", "交清", "减额交清", "免交", "自垫有效"]}]</t>
         </is>
       </c>
       <c r="O343" t="n">
@@ -17162,7 +17161,7 @@
           <t>客户价值标签为B
 并且客户温度为低温
 并且有子女
-并且保单状态为交费有效的客户</t>
+并且保单状态包含交费有效、自垫交清、交清、减额交清、免交、自垫有效的客户</t>
         </is>
       </c>
       <c r="Q343" t="inlineStr">
@@ -17186,7 +17185,7 @@
         <v>0</v>
       </c>
       <c r="H344" t="n">
-        <v>1735.444832942449</v>
+        <v>1576.831709011458</v>
       </c>
       <c r="J344" t="inlineStr">
         <is>
@@ -17236,7 +17235,7 @@
         <v>0</v>
       </c>
       <c r="H345" t="n">
-        <v>1798.024917021394</v>
+        <v>1697.818666929379</v>
       </c>
       <c r="J345" t="inlineStr">
         <is>
@@ -17286,7 +17285,7 @@
         <v>0</v>
       </c>
       <c r="H346" t="n">
-        <v>1920.689042075537</v>
+        <v>1794.299458037131</v>
       </c>
       <c r="J346" t="inlineStr">
         <is>
@@ -17301,7 +17300,7 @@
       </c>
       <c r="N346" s="3" t="inlineStr">
         <is>
-          <t>[{"field": "newValueLabel", "operator": "MATCH", "value": "B"}, {"field": "clientTemperature", "operator": "MATCH", "value": "中温"}, {"field": "mariSts", "operator": "MATCH", "value": "已婚"}, {"field": "assetsCondition", "operator": "CONTAINS", "value": ["有房有车", "有车"]}, {"field": "polNoInfo.polStatus", "operator": "MATCH", "value": "交费有效"}]</t>
+          <t>[{"field": "newValueLabel", "operator": "MATCH", "value": "B"}, {"field": "clientTemperature", "operator": "MATCH", "value": "中温"}, {"field": "mariSts", "operator": "MATCH", "value": "已婚"}, {"field": "assetsCondition", "operator": "CONTAINS", "value": ["有车", "有房有车"]}, {"field": "polNoInfo.polStatus", "operator": "CONTAINS", "value": ["交费有效", "自垫交清", "交清", "减额交清", "免交", "自垫有效"]}]</t>
         </is>
       </c>
       <c r="O346" t="n">
@@ -17312,8 +17311,8 @@
           <t>客户价值标签为B
 并且客户温度为中温
 并且客户婚姻状况为已婚
-并且客户资产状况包含有房有车、有车
-并且保单状态为交费有效的客户</t>
+并且客户资产状况包含有车、有房有车
+并且保单状态包含交费有效、自垫交清、交清、减额交清、免交、自垫有效的客户</t>
         </is>
       </c>
       <c r="Q346" t="inlineStr">
@@ -17337,7 +17336,7 @@
         <v>0</v>
       </c>
       <c r="H347" t="n">
-        <v>1970.575832994655</v>
+        <v>1676.590666058473</v>
       </c>
       <c r="J347" t="inlineStr">
         <is>
@@ -17352,7 +17351,7 @@
       </c>
       <c r="N347" s="3" t="inlineStr">
         <is>
-          <t>[{"field": "clientTemperature", "operator": "MATCH", "value": "高温"}, {"field": "newValueLabel", "operator": "CONTAINS", "value": ["A1", "A2", "A3", "A4", "B"]}, {"field": "familyInfo.familyclientbirthday", "operator": "LTE", "value": "1971-05-19 23:59:59"}, {"field": "polNoInfo.polStatus", "operator": "CONTAINS", "value": ["交费有效", "自垫交清", "交清", "减额交清", "免交", "自垫有效"]}]</t>
+          <t>[{"field": "clientTemperature", "operator": "MATCH", "value": "高温"}, {"field": "newValueLabel", "operator": "MATCH", "value": "B"}, {"field": "familyInfo.familyclientbirthday", "operator": "LTE", "value": "1971-05-20 23:59:59"}, {"field": "polNoInfo.polStatus", "operator": "CONTAINS", "value": ["交费有效", "自垫交清", "交清", "减额交清", "免交", "自垫有效"]}]</t>
         </is>
       </c>
       <c r="O347" t="n">
@@ -17361,7 +17360,7 @@
       <c r="P347" s="3" t="inlineStr">
         <is>
           <t>客户温度为高温
-并且客户价值标签包含A1、A2、A3、A4、B
+并且客户价值标签为B
 并且家庭成员年龄≥55
 并且保单状态包含交费有效、自垫交清、交清、减额交清、免交、自垫有效的客户</t>
         </is>
@@ -17387,7 +17386,7 @@
         <v>0</v>
       </c>
       <c r="H348" t="n">
-        <v>1581.234875018708</v>
+        <v>2286.668249987997</v>
       </c>
       <c r="J348" t="inlineStr">
         <is>
@@ -17438,7 +17437,7 @@
         <v>0</v>
       </c>
       <c r="H349" t="n">
-        <v>1587.319375015795</v>
+        <v>1677.6096659014</v>
       </c>
       <c r="J349" t="inlineStr">
         <is>
@@ -17488,7 +17487,7 @@
         <v>0</v>
       </c>
       <c r="H350" t="n">
-        <v>1316.838833037764</v>
+        <v>1917.811958002858</v>
       </c>
       <c r="J350" t="inlineStr">
         <is>
@@ -17503,7 +17502,7 @@
       </c>
       <c r="N350" s="3" t="inlineStr">
         <is>
-          <t>[{"field": "newValueLabel", "operator": "MATCH", "value": "A1"}, {"field": "clientTemperature", "operator": "MATCH", "value": "中温"}, {"field": "mariSts", "operator": "CONTAINS", "value": ["未婚", "离婚"]}, {"field": "familyInfo.familyrelation", "operator": "NOT_CONTAINS", "value": ["子女"]}, {"field": "polNoInfo.polStatus", "operator": "MATCH", "value": "交费有效"}]</t>
+          <t>[{"field": "newValueLabel", "operator": "MATCH", "value": "A1"}, {"field": "clientTemperature", "operator": "MATCH", "value": "中温"}, {"field": "mariSts", "operator": "CONTAINS", "value": ["未婚", "离婚"]}, {"field": "familyInfo.familyrelation", "operator": "NOT_CONTAINS", "value": ["子女"]}, {"field": "polNoInfo.polStatus", "operator": "CONTAINS", "value": ["交费有效", "自垫交清", "交清", "减额交清", "免交", "自垫有效"]}]</t>
         </is>
       </c>
       <c r="O350" t="n">
@@ -17515,7 +17514,7 @@
 并且客户温度为中温
 并且客户婚姻状况包含未婚、离婚
 并且没有子女
-并且保单状态为交费有效的客户</t>
+并且保单状态包含交费有效、自垫交清、交清、减额交清、免交、自垫有效的客户</t>
         </is>
       </c>
       <c r="Q350" t="inlineStr">
@@ -17539,7 +17538,7 @@
         <v>0</v>
       </c>
       <c r="H351" t="n">
-        <v>1099.082082975656</v>
+        <v>1504.304833011702</v>
       </c>
       <c r="J351" t="inlineStr">
         <is>
@@ -17588,7 +17587,7 @@
         <v>0</v>
       </c>
       <c r="H352" t="n">
-        <v>1405.413875007071</v>
+        <v>1491.778124938719</v>
       </c>
       <c r="J352" t="inlineStr">
         <is>
@@ -17637,7 +17636,7 @@
         <v>0</v>
       </c>
       <c r="H353" t="n">
-        <v>1435.066708014347</v>
+        <v>1362.993124988861</v>
       </c>
       <c r="J353" t="inlineStr">
         <is>
@@ -17652,7 +17651,7 @@
       </c>
       <c r="N353" s="3" t="inlineStr">
         <is>
-          <t>[{"field": "clientAge", "operator": "GTE", "value": 51}, {"field": "newValueLabel", "operator": "MATCH", "value": "B"}]</t>
+          <t>[{"field": "clientAge", "operator": "GTE", "value": 50}, {"field": "newValueLabel", "operator": "MATCH", "value": "B"}]</t>
         </is>
       </c>
       <c r="O353" t="n">
@@ -17660,7 +17659,7 @@
       </c>
       <c r="P353" s="3" t="inlineStr">
         <is>
-          <t>客户年龄≥51
+          <t>客户年龄≥50
 并且客户价值标签为B的客户
 提示：犹豫期时间暂不支持搜索，系统将按可支持字段搜索。</t>
         </is>
@@ -17686,7 +17685,7 @@
         <v>0</v>
       </c>
       <c r="H354" t="n">
-        <v>2122.160291997716</v>
+        <v>1851.646958035417</v>
       </c>
       <c r="J354" t="inlineStr">
         <is>
@@ -17735,7 +17734,7 @@
         <v>0</v>
       </c>
       <c r="H355" t="n">
-        <v>1366.765458020382</v>
+        <v>1616.174999973737</v>
       </c>
       <c r="J355" t="inlineStr">
         <is>
@@ -17784,7 +17783,7 @@
         <v>0</v>
       </c>
       <c r="H356" t="n">
-        <v>1313.837915891781</v>
+        <v>1375.357124954462</v>
       </c>
       <c r="J356" t="inlineStr">
         <is>
@@ -17833,7 +17832,7 @@
         <v>0</v>
       </c>
       <c r="H357" t="n">
-        <v>1539.351750048809</v>
+        <v>1358.992957975715</v>
       </c>
       <c r="J357" t="inlineStr">
         <is>
@@ -17848,7 +17847,7 @@
       </c>
       <c r="N357" s="3" t="inlineStr">
         <is>
-          <t>[{"field": "clientAge", "operator": "GTE", "value": 51}, {"field": "newValueLabel", "operator": "MATCH", "value": "A1"}, {"field": "polNoInfo.polStatus", "operator": "MATCH", "value": "停效"}]</t>
+          <t>[{"field": "clientAge", "operator": "GTE", "value": 50}, {"field": "newValueLabel", "operator": "MATCH", "value": "A1"}, {"field": "polNoInfo.polStatus", "operator": "MATCH", "value": "停效"}]</t>
         </is>
       </c>
       <c r="O357" t="n">
@@ -17856,7 +17855,7 @@
       </c>
       <c r="P357" s="3" t="inlineStr">
         <is>
-          <t>客户年龄≥51
+          <t>客户年龄≥50
 并且客户价值标签为A1
 并且保单状态为停效的客户</t>
         </is>
@@ -17882,7 +17881,7 @@
         <v>0</v>
       </c>
       <c r="H358" t="n">
-        <v>1425.226999912411</v>
+        <v>1589.176625013351</v>
       </c>
       <c r="J358" t="inlineStr">
         <is>
@@ -17931,7 +17930,7 @@
         <v>0</v>
       </c>
       <c r="H359" t="n">
-        <v>1286.632166011259</v>
+        <v>1521.3575840462</v>
       </c>
       <c r="J359" t="inlineStr">
         <is>
@@ -17980,7 +17979,7 @@
         <v>0</v>
       </c>
       <c r="H360" t="n">
-        <v>1597.298832959495</v>
+        <v>1471.520834020339</v>
       </c>
       <c r="J360" t="inlineStr">
         <is>
@@ -17995,7 +17994,7 @@
       </c>
       <c r="N360" s="3" t="inlineStr">
         <is>
-          <t>[{"field": "clientAge", "operator": "GTE", "value": 45}, {"field": "clientTemperature", "operator": "MATCH", "value": "低温"}, {"field": "polNoInfo.polStatus", "operator": "CONTAINS", "value": ["交费有效", "自垫交清", "交清", "减额交清", "免交", "自垫有效"]}]</t>
+          <t>[{"field": "clientAge", "operator": "GTE", "value": 45}, {"field": "clientTemperature", "operator": "MATCH", "value": "低温"}, {"field": "polNoInfo.polStatus", "operator": "MATCH", "value": "交费有效"}]</t>
         </is>
       </c>
       <c r="O360" t="n">
@@ -18005,7 +18004,7 @@
         <is>
           <t>客户年龄≥45
 并且客户温度为低温
-并且保单状态包含交费有效、自垫交清、交清、减额交清、免交、自垫有效的客户</t>
+并且保单状态为交费有效的客户</t>
         </is>
       </c>
       <c r="Q360" t="inlineStr">
@@ -18029,7 +18028,7 @@
         <v>0</v>
       </c>
       <c r="H361" t="n">
-        <v>1310.781624983065</v>
+        <v>1795.032207970507</v>
       </c>
       <c r="J361" t="inlineStr">
         <is>
@@ -18078,7 +18077,7 @@
         <v>0</v>
       </c>
       <c r="H362" t="n">
-        <v>1115.865041036159</v>
+        <v>1378.559125005268</v>
       </c>
       <c r="J362" t="inlineStr">
         <is>
@@ -18127,7 +18126,7 @@
         <v>0</v>
       </c>
       <c r="H363" t="n">
-        <v>1085.059709032066</v>
+        <v>1278.195874998346</v>
       </c>
       <c r="J363" t="inlineStr">
         <is>
@@ -18176,7 +18175,7 @@
         <v>0</v>
       </c>
       <c r="H364" t="n">
-        <v>1371.246124967001</v>
+        <v>1683.329457999207</v>
       </c>
       <c r="J364" t="inlineStr">
         <is>
@@ -18225,7 +18224,7 @@
         <v>0</v>
       </c>
       <c r="H365" t="n">
-        <v>1323.599208961241</v>
+        <v>1363.095749984495</v>
       </c>
       <c r="J365" t="inlineStr">
         <is>
@@ -18274,7 +18273,7 @@
         <v>0</v>
       </c>
       <c r="H366" t="n">
-        <v>1283.374542021193</v>
+        <v>1668.934999965131</v>
       </c>
       <c r="J366" t="inlineStr">
         <is>
@@ -18324,7 +18323,7 @@
         <v>0</v>
       </c>
       <c r="H367" t="n">
-        <v>1705.57133294642</v>
+        <v>1627.267417032272</v>
       </c>
       <c r="J367" t="inlineStr">
         <is>
@@ -18373,7 +18372,7 @@
         <v>0</v>
       </c>
       <c r="H368" t="n">
-        <v>1415.624834015034</v>
+        <v>1541.976582957432</v>
       </c>
       <c r="J368" t="inlineStr">
         <is>
@@ -18423,7 +18422,7 @@
         <v>0</v>
       </c>
       <c r="H369" t="n">
-        <v>1827.952708932571</v>
+        <v>1641.689458978362</v>
       </c>
       <c r="J369" t="inlineStr">
         <is>
@@ -18472,7 +18471,7 @@
         <v>0</v>
       </c>
       <c r="H370" t="n">
-        <v>1160.843124962412</v>
+        <v>1607.045458978973</v>
       </c>
       <c r="J370" t="inlineStr">
         <is>
@@ -18521,7 +18520,7 @@
         <v>0</v>
       </c>
       <c r="H371" t="n">
-        <v>1338.542500045151</v>
+        <v>1641.742042033002</v>
       </c>
       <c r="J371" t="inlineStr">
         <is>
@@ -18570,7 +18569,7 @@
         <v>0</v>
       </c>
       <c r="H372" t="n">
-        <v>1220.843374961987</v>
+        <v>1674.207082949579</v>
       </c>
       <c r="J372" t="inlineStr">
         <is>
@@ -18619,7 +18618,7 @@
         <v>0</v>
       </c>
       <c r="H373" t="n">
-        <v>2042.539166053757</v>
+        <v>1642.704332945868</v>
       </c>
       <c r="J373" t="inlineStr">
         <is>
@@ -18634,7 +18633,7 @@
       </c>
       <c r="N373" s="3" t="inlineStr">
         <is>
-          <t>[{"field": "clientAge", "operator": "RANGE", "value": {"max": 35, "min": 35}}, {"field": "pCategorys", "operator": "NOT_CONTAINS", "value": ["意外伤害保险", "医疗保险", "护理保险", "疾病保险", "定期寿险", "终身寿险"]}, {"field": "polNoInfo.polStatus", "operator": "MATCH", "value": "交费有效"}]</t>
+          <t>[{"field": "clientAge", "operator": "RANGE", "value": {"max": 35, "min": 35}}, {"field": "pCategorys", "operator": "MATCH", "value": "意外伤害保险"}, {"field": "polNoInfo.polStatus", "operator": "MATCH", "value": "交费有效"}]</t>
         </is>
       </c>
       <c r="O373" t="n">
@@ -18643,7 +18642,7 @@
       <c r="P373" s="3" t="inlineStr">
         <is>
           <t>客户年龄=35
-并且产品类别不包含意外伤害保险、医疗保险、护理保险、疾病保险、定期寿险、终身寿险
+并且产品类别为意外伤害保险
 并且保单状态为交费有效的客户</t>
         </is>
       </c>
@@ -18668,7 +18667,7 @@
         <v>0</v>
       </c>
       <c r="H374" t="n">
-        <v>1618.202209006995</v>
+        <v>2101.130124996416</v>
       </c>
       <c r="J374" t="inlineStr">
         <is>
@@ -18717,7 +18716,7 @@
         <v>0</v>
       </c>
       <c r="H375" t="n">
-        <v>1227.176957996562</v>
+        <v>1515.291666961275</v>
       </c>
       <c r="J375" t="inlineStr">
         <is>
@@ -18766,7 +18765,7 @@
         <v>0</v>
       </c>
       <c r="H376" t="n">
-        <v>1254.722625017166</v>
+        <v>1498.820709064603</v>
       </c>
       <c r="J376" t="inlineStr">
         <is>
@@ -18815,7 +18814,7 @@
         <v>0</v>
       </c>
       <c r="H377" t="n">
-        <v>1476.737832999788</v>
+        <v>1399.691209080629</v>
       </c>
       <c r="J377" t="inlineStr">
         <is>
@@ -18830,7 +18829,7 @@
       </c>
       <c r="N377" s="3" t="inlineStr">
         <is>
-          <t>[{"field": "clientAge", "operator": "LTE", "value": 44}, {"field": "polNoInfo.plancodeinfo.abbrname", "operator": "MATCH", "value": "e生保"}, {"field": "polNoInfo.polStatus", "operator": "MATCH", "value": "交费有效"}]</t>
+          <t>[{"field": "clientAge", "operator": "LTE", "value": 45}, {"field": "polNoInfo.plancodeinfo.abbrname", "operator": "MATCH", "value": "e生保"}, {"field": "polNoInfo.polStatus", "operator": "MATCH", "value": "交费有效"}]</t>
         </is>
       </c>
       <c r="O377" t="n">
@@ -18838,7 +18837,7 @@
       </c>
       <c r="P377" s="3" t="inlineStr">
         <is>
-          <t>客户年龄≤44
+          <t>客户年龄≤45
 并且投保险种简称为e生保
 并且保单状态为交费有效的客户</t>
         </is>
@@ -18864,7 +18863,7 @@
         <v>0</v>
       </c>
       <c r="H378" t="n">
-        <v>1758.809208986349</v>
+        <v>1842.803374980576</v>
       </c>
       <c r="J378" t="inlineStr">
         <is>
@@ -18913,7 +18912,7 @@
         <v>0</v>
       </c>
       <c r="H379" t="n">
-        <v>1536.771500017494</v>
+        <v>1617.268375004642</v>
       </c>
       <c r="J379" t="inlineStr">
         <is>
@@ -18962,7 +18961,7 @@
         <v>0</v>
       </c>
       <c r="H380" t="n">
-        <v>1408.288458012976</v>
+        <v>1589.120332966559</v>
       </c>
       <c r="J380" t="inlineStr">
         <is>
@@ -19011,7 +19010,7 @@
         <v>0</v>
       </c>
       <c r="H381" t="n">
-        <v>1538.93275000155</v>
+        <v>2039.822791004553</v>
       </c>
       <c r="J381" t="inlineStr">
         <is>
@@ -19060,7 +19059,7 @@
         <v>0</v>
       </c>
       <c r="H382" t="n">
-        <v>1160.402833949775</v>
+        <v>1659.570041927509</v>
       </c>
       <c r="J382" t="inlineStr">
         <is>
@@ -19109,7 +19108,7 @@
         <v>0</v>
       </c>
       <c r="H383" t="n">
-        <v>1459.03383300174</v>
+        <v>1622.734792064875</v>
       </c>
       <c r="J383" t="inlineStr">
         <is>
@@ -19158,7 +19157,7 @@
         <v>0</v>
       </c>
       <c r="H384" t="n">
-        <v>1515.032833092846</v>
+        <v>1426.858250051737</v>
       </c>
       <c r="J384" t="inlineStr">
         <is>
@@ -19207,7 +19206,7 @@
         <v>0</v>
       </c>
       <c r="H385" t="n">
-        <v>1195.22875000257</v>
+        <v>1315.565207973123</v>
       </c>
       <c r="J385" t="inlineStr">
         <is>
@@ -19256,7 +19255,7 @@
         <v>0</v>
       </c>
       <c r="H386" t="n">
-        <v>1117.817874997854</v>
+        <v>1569.419290986843</v>
       </c>
       <c r="J386" t="inlineStr">
         <is>
@@ -19305,7 +19304,7 @@
         <v>0</v>
       </c>
       <c r="H387" t="n">
-        <v>1564.359458978288</v>
+        <v>2068.936624913476</v>
       </c>
       <c r="J387" t="inlineStr">
         <is>
@@ -19320,7 +19319,7 @@
       </c>
       <c r="N387" s="3" t="inlineStr">
         <is>
-          <t>[{"field": "clientAge", "operator": "GTE", "value": 45}, {"field": "newValueLabel", "operator": "MATCH", "value": "A1"}, {"field": "clientTemperature", "operator": "MATCH", "value": "高温"}, {"field": "familyInfo.familyrelation", "operator": "MATCH", "value": "子女"}, {"field": "familyInfo.familyclientbirthday", "operator": "RANGE", "value": {"max": "2026-05-19 23:59:59", "min": "2008-05-20 00:00:00"}}, {"field": "polNoInfo.plancodeinfo.abbrname", "operator": "MATCH", "value": "e生保"}]</t>
+          <t>[{"field": "clientAge", "operator": "GTE", "value": 45}, {"field": "newValueLabel", "operator": "MATCH", "value": "A1"}, {"field": "clientTemperature", "operator": "MATCH", "value": "高温"}, {"field": "familyInfo.familyrelation", "operator": "MATCH", "value": "子女"}, {"field": "familyInfo.familyclientbirthday", "operator": "RANGE", "value": {"max": "2026-05-20 23:59:59", "min": "2008-05-21 00:00:00"}}, {"field": "polNoInfo.plancodeinfo.abbrname", "operator": "MATCH", "value": "e生保"}]</t>
         </is>
       </c>
       <c r="O387" t="n">
@@ -19357,7 +19356,7 @@
         <v>0</v>
       </c>
       <c r="H388" t="n">
-        <v>1436.694625066593</v>
+        <v>1744.197290972807</v>
       </c>
       <c r="J388" t="inlineStr">
         <is>
@@ -19408,7 +19407,7 @@
         <v>0</v>
       </c>
       <c r="H389" t="n">
-        <v>1682.520125061274</v>
+        <v>2138.414000044577</v>
       </c>
       <c r="J389" t="inlineStr">
         <is>
@@ -19460,7 +19459,7 @@
         <v>0</v>
       </c>
       <c r="H390" t="n">
-        <v>1833.021042053588</v>
+        <v>2199.445249978453</v>
       </c>
       <c r="J390" t="inlineStr">
         <is>
@@ -19475,7 +19474,7 @@
       </c>
       <c r="N390" s="3" t="inlineStr">
         <is>
-          <t>[{"field": "clientAge", "operator": "RANGE", "value": {"max": 40, "min": 35}}, {"field": "newValueLabel", "operator": "MATCH", "value": "A1"}, {"field": "clientTemperature", "operator": "MATCH", "value": "中温"}, {"field": "polNoInfo.plancodeinfo.abbrname", "operator": "MATCH", "value": "e生保"}, {"field": "polNoInfo.plancodeinfo.plantypedesc", "operator": "MATCH", "value": "年金"}, {"field": "familyInfo.familyrelation", "operator": "MATCH", "value": "子女"}, {"field": "familyInfo.familyclientbirthday", "operator": "RANGE", "value": {"max": "2026-05-19 23:59:59", "min": "2008-05-20 00:00:00"}}]</t>
+          <t>[{"field": "clientAge", "operator": "RANGE", "value": {"max": 40, "min": 35}}, {"field": "newValueLabel", "operator": "MATCH", "value": "A1"}, {"field": "clientTemperature", "operator": "MATCH", "value": "中温"}, {"field": "polNoInfo.plancodeinfo.abbrname", "operator": "MATCH", "value": "e生保"}, {"field": "polNoInfo.plancodeinfo.plantypedesc", "operator": "MATCH", "value": "年金"}, {"field": "familyInfo.familyrelation", "operator": "MATCH", "value": "子女"}, {"field": "familyInfo.familyclientbirthday", "operator": "RANGE", "value": {"max": "2026-05-20 23:59:59", "min": "2008-05-21 00:00:00"}}]</t>
         </is>
       </c>
       <c r="O390" t="n">
@@ -19513,7 +19512,7 @@
         <v>0</v>
       </c>
       <c r="H391" t="n">
-        <v>1581.172207952477</v>
+        <v>1755.867916974239</v>
       </c>
       <c r="J391" t="inlineStr">
         <is>
@@ -19528,7 +19527,7 @@
       </c>
       <c r="N391" s="3" t="inlineStr">
         <is>
-          <t>[{"field": "clientAge", "operator": "GTE", "value": 51}, {"field": "newValueLabel", "operator": "MATCH", "value": "B"}, {"field": "clientTemperature", "operator": "MATCH", "value": "中温"}, {"field": "familyInfo.familyclientbirthday", "operator": "LTE", "value": "1971-05-19 23:59:59"}, {"field": "polNoInfo.plancodeinfo.plantypedesc", "operator": "MATCH", "value": "年金"}]</t>
+          <t>[{"field": "clientAge", "operator": "GTE", "value": 50}, {"field": "newValueLabel", "operator": "MATCH", "value": "B"}, {"field": "clientTemperature", "operator": "MATCH", "value": "中温"}, {"field": "familyInfo.familyclientbirthday", "operator": "LTE", "value": "1971-05-20 23:59:59"}, {"field": "polNoInfo.plancodeinfo.plantypedesc", "operator": "MATCH", "value": "年金"}]</t>
         </is>
       </c>
       <c r="O391" t="n">
@@ -19536,7 +19535,7 @@
       </c>
       <c r="P391" s="3" t="inlineStr">
         <is>
-          <t>客户年龄≥51
+          <t>客户年龄≥50
 并且客户价值标签为B
 并且客户温度为中温
 并且家庭成员年龄≥55
@@ -19564,7 +19563,7 @@
         <v>0</v>
       </c>
       <c r="H392" t="n">
-        <v>1600.212958059274</v>
+        <v>2196.262833080254</v>
       </c>
       <c r="J392" t="inlineStr">
         <is>
@@ -19579,7 +19578,7 @@
       </c>
       <c r="N392" s="3" t="inlineStr">
         <is>
-          <t>[{"field": "clientAge", "operator": "RANGE", "value": {"max": 39, "min": 30}}, {"field": "newValueLabel", "operator": "MATCH", "value": "A2"}, {"field": "clientTemperature", "operator": "MATCH", "value": "低温"}, {"field": "mariSts", "operator": "MATCH", "value": "已婚"}, {"field": "pCategorys", "operator": "MATCH", "value": "意外伤害保险"}]</t>
+          <t>[{"field": "clientAge", "operator": "RANGE", "value": {"max": 39, "min": 30}}, {"field": "newValueLabel", "operator": "MATCH", "value": "A2"}, {"field": "clientTemperature", "operator": "MATCH", "value": "低温"}, {"field": "mariSts", "operator": "MATCH", "value": "已婚"}, {"field": "familyInfo.familyrelation", "operator": "MATCH", "value": "子女"}, {"field": "pCategorys", "operator": "MATCH", "value": "意外伤害保险"}]</t>
         </is>
       </c>
       <c r="O392" t="n">
@@ -19591,6 +19590,7 @@
 并且客户价值标签为A2
 并且客户温度为低温
 并且客户婚姻状况为已婚
+并且有子女
 并且产品类别为意外伤害保险的客户</t>
         </is>
       </c>
@@ -19615,7 +19615,7 @@
         <v>0</v>
       </c>
       <c r="H393" t="n">
-        <v>24.48216592893004</v>
+        <v>19.61904100608081</v>
       </c>
       <c r="J393" t="inlineStr">
         <is>
@@ -19662,7 +19662,7 @@
         <v>0</v>
       </c>
       <c r="H394" t="n">
-        <v>29.72912497352809</v>
+        <v>25.68779198918492</v>
       </c>
       <c r="J394" t="inlineStr">
         <is>
@@ -19709,7 +19709,7 @@
         <v>0</v>
       </c>
       <c r="H395" t="n">
-        <v>13.14595795702189</v>
+        <v>12.47170800343156</v>
       </c>
       <c r="J395" t="inlineStr">
         <is>
@@ -19756,7 +19756,7 @@
         <v>0</v>
       </c>
       <c r="H396" t="n">
-        <v>1105.033125029877</v>
+        <v>1166.986166965216</v>
       </c>
       <c r="J396" t="inlineStr">
         <is>
@@ -19803,7 +19803,7 @@
         <v>0</v>
       </c>
       <c r="H397" t="n">
-        <v>920.6791670294479</v>
+        <v>1020.141207962297</v>
       </c>
       <c r="J397" t="inlineStr">
         <is>
@@ -19850,7 +19850,7 @@
         <v>0</v>
       </c>
       <c r="H398" t="n">
-        <v>18.98275001440197</v>
+        <v>18.35308305453509</v>
       </c>
       <c r="J398" t="inlineStr">
         <is>
@@ -19899,7 +19899,7 @@
         <v>0</v>
       </c>
       <c r="H399" t="n">
-        <v>1477.047833031975</v>
+        <v>1543.163500027731</v>
       </c>
       <c r="J399" t="inlineStr">
         <is>
@@ -19914,7 +19914,7 @@
       </c>
       <c r="N399" s="3" t="inlineStr">
         <is>
-          <t>[{"field": "idValidDate", "operator": "RANGE", "value": {"max": "2026-06-19 00:00:00", "min": "2026-05-20 00:00:00"}}]</t>
+          <t>[{"field": "idValidDate", "operator": "RANGE", "value": {"max": "2026-06-20 00:00:00", "min": "2026-05-21 00:00:00"}}]</t>
         </is>
       </c>
       <c r="O399" t="n">
@@ -19922,7 +19922,7 @@
       </c>
       <c r="P399" s="3" t="inlineStr">
         <is>
-          <t>证件有效期在2026-05-20 至 2026-06-19的客户</t>
+          <t>证件有效期在2026-05-21 至 2026-06-20的客户</t>
         </is>
       </c>
       <c r="Q399" t="inlineStr">
@@ -19946,7 +19946,7 @@
         <v>0</v>
       </c>
       <c r="H400" t="n">
-        <v>16.66304201353341</v>
+        <v>20.24783298838884</v>
       </c>
       <c r="J400" t="inlineStr">
         <is>
@@ -19993,7 +19993,7 @@
         <v>0</v>
       </c>
       <c r="H401" t="n">
-        <v>1449.886874994263</v>
+        <v>1543.339916970581</v>
       </c>
       <c r="J401" t="inlineStr">
         <is>
@@ -20017,7 +20017,7 @@
       <c r="P401" s="3" t="inlineStr">
         <is>
           <t>保单状态为犹豫期退保的客户
-提示：退保时间暂不支持搜索，系统将按可支持字段搜索。</t>
+提示：犹豫期时间暂不支持搜索，系统将按可支持字段搜索。</t>
         </is>
       </c>
       <c r="Q401" t="inlineStr">
@@ -20041,7 +20041,7 @@
         <v>0</v>
       </c>
       <c r="H402" t="n">
-        <v>33.53633300866932</v>
+        <v>27.54133299458772</v>
       </c>
       <c r="J402" t="inlineStr">
         <is>
@@ -20056,7 +20056,7 @@
       </c>
       <c r="N402" s="3" t="inlineStr">
         <is>
-          <t>[{"field": "familyInfo.familyclientbirthday", "operator": "RANGE", "value": {"max": "2008-05-19 23:59:59", "min": "2003-05-20 00:00:00"}}, {"field": "familyInfo.familyrelation", "operator": "MATCH", "value": "子女"}, {"field": "familyInfo.familyclientsex", "operator": "MATCH", "value": "女"}]</t>
+          <t>[{"field": "familyInfo.familyclientbirthday", "operator": "RANGE", "value": {"max": "2008-05-20 23:59:59", "min": "2003-05-21 00:00:00"}}, {"field": "familyInfo.familyrelation", "operator": "MATCH", "value": "子女"}, {"field": "familyInfo.familyclientsex", "operator": "MATCH", "value": "女"}]</t>
         </is>
       </c>
       <c r="O402" t="n">
@@ -20090,7 +20090,7 @@
         <v>0</v>
       </c>
       <c r="H403" t="n">
-        <v>36.43474995624274</v>
+        <v>14.40120802726597</v>
       </c>
       <c r="J403" t="inlineStr">
         <is>
@@ -20105,7 +20105,7 @@
       </c>
       <c r="N403" s="3" t="inlineStr">
         <is>
-          <t>[{"field": "familyInfo.familyclientbirthday", "operator": "RANGE", "value": {"max": "2020-05-19 23:59:59", "min": "2013-05-20 00:00:00"}}, {"field": "familyInfo.familyrelation", "operator": "MATCH", "value": "子女"}]</t>
+          <t>[{"field": "familyInfo.familyclientbirthday", "operator": "RANGE", "value": {"max": "2020-05-20 23:59:59", "min": "2013-05-21 00:00:00"}}, {"field": "familyInfo.familyrelation", "operator": "MATCH", "value": "子女"}]</t>
         </is>
       </c>
       <c r="O403" t="n">
@@ -20138,7 +20138,7 @@
         <v>0</v>
       </c>
       <c r="H404" t="n">
-        <v>1077.284459024668</v>
+        <v>1234.32608298026</v>
       </c>
       <c r="J404" t="inlineStr">
         <is>
@@ -20186,7 +20186,7 @@
         <v>0</v>
       </c>
       <c r="H405" t="n">
-        <v>1198.446082998998</v>
+        <v>1490.23987504188</v>
       </c>
       <c r="J405" t="inlineStr">
         <is>
@@ -20235,7 +20235,7 @@
         <v>0</v>
       </c>
       <c r="H406" t="n">
-        <v>1299.378540948965</v>
+        <v>1529.42220796831</v>
       </c>
       <c r="J406" t="inlineStr">
         <is>
@@ -20250,7 +20250,7 @@
       </c>
       <c r="N406" s="3" t="inlineStr">
         <is>
-          <t>[{"field": "newValueLabel", "operator": "MATCH", "value": "B"}, {"field": "polNoInfo.plancodeinfo.plantypedesc", "operator": "MATCH", "value": "年金"}, {"field": "familyInfo.familyrelation", "operator": "MATCH", "value": "子女"}, {"field": "familyInfo.familyclientsex", "operator": "MATCH", "value": "女"}]</t>
+          <t>[{"field": "newValueLabel", "operator": "MATCH", "value": "B"}, {"field": "pCategorys", "operator": "MATCH", "value": "年金保险"}, {"field": "familyInfo.familyrelation", "operator": "MATCH", "value": "子女"}, {"field": "familyInfo.familyclientsex", "operator": "MATCH", "value": "女"}]</t>
         </is>
       </c>
       <c r="O406" t="n">
@@ -20259,7 +20259,7 @@
       <c r="P406" s="3" t="inlineStr">
         <is>
           <t>客户价值标签为B
-并且投保险种类别为年金
+并且产品类别为年金保险
 并且有子女
 并且子女性别为女的客户</t>
         </is>
@@ -20285,7 +20285,7 @@
         <v>0</v>
       </c>
       <c r="H407" t="n">
-        <v>1711.556249996647</v>
+        <v>1599.940416985191</v>
       </c>
       <c r="J407" t="inlineStr">
         <is>
@@ -20336,7 +20336,7 @@
         <v>0</v>
       </c>
       <c r="H408" t="n">
-        <v>1385.791208012961</v>
+        <v>1429.436209029518</v>
       </c>
       <c r="J408" t="inlineStr">
         <is>
@@ -20385,7 +20385,7 @@
         <v>0</v>
       </c>
       <c r="H409" t="n">
-        <v>1488.210832932964</v>
+        <v>2345.130708999932</v>
       </c>
       <c r="J409" t="inlineStr">
         <is>
@@ -20434,7 +20434,7 @@
         <v>0</v>
       </c>
       <c r="H410" t="n">
-        <v>1423.36954199709</v>
+        <v>1622.19558400102</v>
       </c>
       <c r="J410" t="inlineStr">
         <is>
@@ -20483,7 +20483,7 @@
         <v>0</v>
       </c>
       <c r="H411" t="n">
-        <v>1306.214249925688</v>
+        <v>1713.357000029646</v>
       </c>
       <c r="J411" t="inlineStr">
         <is>
@@ -20533,7 +20533,7 @@
         <v>0</v>
       </c>
       <c r="H412" t="n">
-        <v>1532.184874988161</v>
+        <v>1764.830917003565</v>
       </c>
       <c r="J412" t="inlineStr">
         <is>
@@ -20583,7 +20583,7 @@
         <v>0</v>
       </c>
       <c r="H413" t="n">
-        <v>1736.330582993105</v>
+        <v>2581.573624978773</v>
       </c>
       <c r="J413" t="inlineStr">
         <is>
@@ -20633,7 +20633,7 @@
         <v>0</v>
       </c>
       <c r="H414" t="n">
-        <v>1906.718792044558</v>
+        <v>1713.914374937303</v>
       </c>
       <c r="J414" t="inlineStr">
         <is>
@@ -20683,7 +20683,7 @@
         <v>0</v>
       </c>
       <c r="H415" t="n">
-        <v>1850.519416038878</v>
+        <v>1858.347458997741</v>
       </c>
       <c r="J415" t="inlineStr">
         <is>
@@ -20698,7 +20698,7 @@
       </c>
       <c r="N415" s="3" t="inlineStr">
         <is>
-          <t>[{"field": "newValueLabel", "operator": "MATCH", "value": "A1"}, {"field": "clientTemperature", "operator": "MATCH", "value": "高温"}, {"field": "familyInfo.familyrelation", "operator": "MATCH", "value": "子女"}, {"field": "familyInfo.familyclientbirthday", "operator": "RANGE", "value": {"max": "2026-05-19 23:59:59", "min": "2008-05-20 00:00:00"}}, {"field": "polNoInfo.polStatus", "operator": "CONTAINS", "value": ["交费有效", "自垫交清", "交清", "减额交清", "免交", "自垫有效"]}]</t>
+          <t>[{"field": "newValueLabel", "operator": "MATCH", "value": "A1"}, {"field": "clientTemperature", "operator": "MATCH", "value": "高温"}, {"field": "familyInfo.familyrelation", "operator": "MATCH", "value": "子女"}, {"field": "familyInfo.familyclientbirthday", "operator": "RANGE", "value": {"max": "2026-05-20 23:59:59", "min": "2008-05-21 00:00:00"}}, {"field": "polNoInfo.polStatus", "operator": "CONTAINS", "value": ["交费有效", "自垫交清", "交清", "减额交清", "免交", "自垫有效"]}]</t>
         </is>
       </c>
       <c r="O415" t="n">
@@ -20734,7 +20734,7 @@
         <v>0</v>
       </c>
       <c r="H416" t="n">
-        <v>1516.383957932703</v>
+        <v>1424.565209075809</v>
       </c>
       <c r="J416" t="inlineStr">
         <is>
@@ -20784,7 +20784,7 @@
         <v>0</v>
       </c>
       <c r="H417" t="n">
-        <v>1451.242083101533</v>
+        <v>2458.266499917954</v>
       </c>
       <c r="J417" t="inlineStr">
         <is>
@@ -20835,7 +20835,7 @@
         <v>0</v>
       </c>
       <c r="H418" t="n">
-        <v>2171.273541054688</v>
+        <v>1813.869290985167</v>
       </c>
       <c r="J418" t="inlineStr">
         <is>
@@ -20885,7 +20885,7 @@
         <v>0</v>
       </c>
       <c r="H419" t="n">
-        <v>1875.655875075608</v>
+        <v>1690.201666904613</v>
       </c>
       <c r="J419" t="inlineStr">
         <is>
@@ -20934,7 +20934,7 @@
         <v>0</v>
       </c>
       <c r="H420" t="n">
-        <v>1245.669374940917</v>
+        <v>2321.906832978129</v>
       </c>
       <c r="J420" t="inlineStr">
         <is>
@@ -20949,7 +20949,7 @@
       </c>
       <c r="N420" s="3" t="inlineStr">
         <is>
-          <t>[{"field": "clientAge", "operator": "GTE", "value": 61}, {"field": "newValueLabel", "operator": "MATCH", "value": "A1"}, {"field": "trusteeshipFlag", "operator": "MATCH", "value": "是"}]</t>
+          <t>[{"field": "clientAge", "operator": "GTE", "value": 60}, {"field": "newValueLabel", "operator": "MATCH", "value": "A1"}, {"field": "trusteeshipFlag", "operator": "MATCH", "value": "是"}]</t>
         </is>
       </c>
       <c r="O420" t="n">
@@ -20957,7 +20957,7 @@
       </c>
       <c r="P420" s="3" t="inlineStr">
         <is>
-          <t>客户年龄≥61
+          <t>客户年龄≥60
 并且客户价值标签为A1
 并且托管标志为是的客户</t>
         </is>
@@ -20983,7 +20983,7 @@
         <v>0</v>
       </c>
       <c r="H421" t="n">
-        <v>1366.523583070375</v>
+        <v>1573.719416046515</v>
       </c>
       <c r="J421" t="inlineStr">
         <is>
@@ -21032,7 +21032,7 @@
         <v>0</v>
       </c>
       <c r="H422" t="n">
-        <v>1655.994375003502</v>
+        <v>2108.539875014685</v>
       </c>
       <c r="J422" t="inlineStr">
         <is>
@@ -21047,7 +21047,7 @@
       </c>
       <c r="N422" s="3" t="inlineStr">
         <is>
-          <t>[{"field": "clientAge", "operator": "GTE", "value": 51}, {"field": "newValueLabel", "operator": "MATCH", "value": "B"}, {"field": "familyInfo.familyrelation", "operator": "MATCH", "value": "父母"}, {"field": "polNoInfo.plancodeinfo.plantypedesc", "operator": "MATCH", "value": "年金"}, {"field": "polNoInfo.polStatus", "operator": "CONTAINS", "value": ["交费有效", "自垫交清", "交清", "减额交清", "免交", "自垫有效"]}]</t>
+          <t>[{"field": "clientAge", "operator": "GTE", "value": 50}, {"field": "newValueLabel", "operator": "MATCH", "value": "B"}, {"field": "familyInfo.familyclientbirthday", "operator": "LTE", "value": "1971-05-20 23:59:59"}, {"field": "polNoInfo.plancodeinfo.plantypedesc", "operator": "MATCH", "value": "年金"}, {"field": "polNoInfo.polStatus", "operator": "CONTAINS", "value": ["交费有效", "自垫交清", "交清", "减额交清", "免交", "自垫有效"]}]</t>
         </is>
       </c>
       <c r="O422" t="n">
@@ -21055,9 +21055,9 @@
       </c>
       <c r="P422" s="3" t="inlineStr">
         <is>
-          <t>客户年龄≥51
+          <t>客户年龄≥50
 并且客户价值标签为B
-并且有父母
+并且家庭成员年龄≥55
 并且投保险种类别为年金
 并且保单状态包含交费有效、自垫交清、交清、减额交清、免交、自垫有效的客户</t>
         </is>
@@ -21083,7 +21083,7 @@
         <v>0</v>
       </c>
       <c r="H423" t="n">
-        <v>2185.434707906097</v>
+        <v>2419.637707993388</v>
       </c>
       <c r="J423" t="inlineStr">
         <is>
@@ -21134,7 +21134,7 @@
         <v>0</v>
       </c>
       <c r="H424" t="n">
-        <v>1689.727334072813</v>
+        <v>2739.375500008464</v>
       </c>
       <c r="J424" t="inlineStr">
         <is>
@@ -21149,7 +21149,7 @@
       </c>
       <c r="N424" s="3" t="inlineStr">
         <is>
-          <t>[{"field": "clientAge", "operator": "GTE", "value": 45}, {"field": "clientTemperature", "operator": "MATCH", "value": "高温"}, {"field": "newValueLabel", "operator": "MATCH", "value": "B"}, {"field": "assetsCondition", "operator": "MATCH", "value": "有房有车"}, {"field": "pCategorys", "operator": "MATCH", "value": "疾病保险"}, {"field": "isBuyInsuranceCar", "operator": "MATCH", "value": "车险"}]</t>
+          <t>[{"field": "clientAge", "operator": "GTE", "value": 45}, {"field": "clientTemperature", "operator": "MATCH", "value": "高温"}, {"field": "newValueLabel", "operator": "MATCH", "value": "B"}, {"field": "assetsCondition", "operator": "CONTAINS", "value": ["有车", "有房有车"]}, {"field": "pCategorys", "operator": "MATCH", "value": "疾病保险"}, {"field": "isBuyInsuranceCar", "operator": "MATCH", "value": "车险"}]</t>
         </is>
       </c>
       <c r="O424" t="n">
@@ -21160,7 +21160,7 @@
           <t>客户年龄≥45
 并且客户温度为高温
 并且客户价值标签为B
-并且客户资产状况为有房有车
+并且客户资产状况包含有车、有房有车
 并且产品类别为疾病保险
 并且车险客户</t>
         </is>
@@ -21186,7 +21186,7 @@
         <v>0</v>
       </c>
       <c r="H425" t="n">
-        <v>15.45624993741512</v>
+        <v>11.6146249929443</v>
       </c>
       <c r="J425" t="inlineStr">
         <is>
@@ -21233,7 +21233,7 @@
         <v>0</v>
       </c>
       <c r="H426" t="n">
-        <v>13.03679193370044</v>
+        <v>11.36916701216251</v>
       </c>
       <c r="J426" t="inlineStr">
         <is>
@@ -21280,7 +21280,7 @@
         <v>0</v>
       </c>
       <c r="H427" t="n">
-        <v>877.3846669355407</v>
+        <v>1292.955750017427</v>
       </c>
       <c r="J427" t="inlineStr">
         <is>
@@ -21327,7 +21327,7 @@
         <v>0</v>
       </c>
       <c r="H428" t="n">
-        <v>23.18312495481223</v>
+        <v>17.01504201628268</v>
       </c>
       <c r="J428" t="inlineStr">
         <is>
